--- a/Översikt TRANEMO.xlsx
+++ b/Översikt TRANEMO.xlsx
@@ -601,7 +601,7 @@
         <v>45523</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45132</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45450</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45087</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45917</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>44770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44739</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44767</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>44658</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45377</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>45397</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44770</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>44732</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>46072</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45621</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>44609</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>44848</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45575</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45906</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>45922</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>44866</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3967,7 +3967,7 @@
         <v>44644</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4072,7 +4072,7 @@
         <v>45392</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44947</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45096</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>46244</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>46126</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         <v>45328</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45093</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4825,7 +4825,7 @@
         <v>45800</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45740</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>45831</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45422</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>44706</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44706</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>45638</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45147</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44800</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44564</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>44461</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6056,7 +6056,7 @@
         <v>44585</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44472</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44637</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44487</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6353,7 +6353,7 @@
         <v>44852</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44599</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44851</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44734</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6650,7 +6650,7 @@
         <v>44670</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44494</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44804</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44530</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44616</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44583</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44887</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44502</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44585</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44495</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44537</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>44589</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44675</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44722</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44775</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44599</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44509</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44799</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44680</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44630</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44793</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44800</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>44732</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44882</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44530</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44837</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44469</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44481</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44788</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>44522</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44500</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44705</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44735</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44599</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44552</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>44593</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>44958</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>44596</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>45316</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45196</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>45362</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44998</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>45315</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44656</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>45641</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45157</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>45747</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45747</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>45270</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>44732</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>44882</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>45713</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>45315</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>44947</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>45327</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>45484</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>45740</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>45377</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>45551</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>44852</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>45363</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>45566</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44902</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44867</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>44931</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>45701</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>45574</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11649,7 +11649,7 @@
         <v>45426</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11722,7 +11722,7 @@
         <v>45259</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>45224</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>45257</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11946,7 +11946,7 @@
         <v>45301</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12019,7 +12019,7 @@
         <v>45572</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12092,7 +12092,7 @@
         <v>45694</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>44866</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>45467</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45093</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>44988</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45251</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45044</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>44537</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>44867</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44799</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45227</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45317</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45751</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>45763</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13129,7 +13129,7 @@
         <v>45155</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13202,7 +13202,7 @@
         <v>44983</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13275,7 +13275,7 @@
         <v>45222</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44958</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>45099</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>45763</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45544</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>45174</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13713,7 +13713,7 @@
         <v>44583</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>45747</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13859,7 +13859,7 @@
         <v>45747</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13932,7 +13932,7 @@
         <v>45734</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>45566</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14078,7 +14078,7 @@
         <v>45096</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>45079</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14224,7 +14224,7 @@
         <v>45259</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>45316</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>45245</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45467</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>45222</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44855</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45891</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>44904</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>44578</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45436</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>45183</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>45813</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>45140</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>45587</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>45701</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>44819</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>45762</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>44544</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45785</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45153</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>45714</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45245</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>45399</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>45062</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>45894</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>45425</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>45362</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>45897</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16273,7 +16273,7 @@
         <v>45897</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45897</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16429,7 +16429,7 @@
         <v>45715</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>45743</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>45819</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>44958</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16721,7 +16721,7 @@
         <v>45673</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>45825</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44748</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>45227</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45716</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>44749</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45906</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45670</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>45810</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45912</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>45720</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>45359</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>45917</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45917</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45922</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45547</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45321</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45425</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18055,7 +18055,7 @@
         <v>45096</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
         <v>45096</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>44867</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18274,7 +18274,7 @@
         <v>45169</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>45679</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45740</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45740</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>45933</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45933</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>45936</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45937</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45484</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45937</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>45937</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45939</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19150,7 +19150,7 @@
         <v>45939</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19223,7 +19223,7 @@
         <v>45939</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19296,7 +19296,7 @@
         <v>45937</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45939</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>45939</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>45938</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>45897</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>44977</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45644</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45211</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45315</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>45315</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>45950</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45950</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45950</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>45950</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45950</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>44963</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45329</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>44522</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>44866</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>44838</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>45558</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>44958</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>44578</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>45546</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45966</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45362</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>45359</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>45342</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45034</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45174</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>45978</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45978</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>45978</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>45978</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>45978</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>45978</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>45978</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>45978</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>45978</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>45978</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22299,7 +22299,7 @@
         <v>45390</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22377,7 +22377,7 @@
         <v>45980</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22450,7 +22450,7 @@
         <v>44958</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>45722</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22596,7 +22596,7 @@
         <v>44658</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22669,7 +22669,7 @@
         <v>45624</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22742,7 +22742,7 @@
         <v>44970</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>45989</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>45993</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>45096</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23107,7 +23107,7 @@
         <v>45187</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>46160</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23253,7 +23253,7 @@
         <v>46160</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>46160</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>45392</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>45679</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>45679</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>45424</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23691,7 +23691,7 @@
         <v>45424</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23764,7 +23764,7 @@
         <v>44462</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23837,7 +23837,7 @@
         <v>45994</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23910,7 +23910,7 @@
         <v>45994</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23983,7 +23983,7 @@
         <v>44866</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24061,7 +24061,7 @@
         <v>45303</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24134,7 +24134,7 @@
         <v>45170</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>44965</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>44552</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24353,7 +24353,7 @@
         <v>46000</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24426,7 +24426,7 @@
         <v>44720</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24499,7 +24499,7 @@
         <v>44882</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44652</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>44882</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45551</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>45316</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24864,7 +24864,7 @@
         <v>46010</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>46013</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>46013</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25083,7 +25083,7 @@
         <v>46013</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25156,7 +25156,7 @@
         <v>46013</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25229,7 +25229,7 @@
         <v>45772</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45714</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45705</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>45720</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>45695</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45701</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25667,7 +25667,7 @@
         <v>45711</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45688</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25813,7 +25813,7 @@
         <v>45715</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45714</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>44665</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45656</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26105,7 +26105,7 @@
         <v>45188</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45574</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26251,7 +26251,7 @@
         <v>44867</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26324,7 +26324,7 @@
         <v>45140</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45463</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26470,7 +26470,7 @@
         <v>45463</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45665</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45922</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>44656</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44600</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45526</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>45316</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26981,7 +26981,7 @@
         <v>46174</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>45664</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27127,7 +27127,7 @@
         <v>45673</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27200,7 +27200,7 @@
         <v>46176</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>45002</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27346,7 +27346,7 @@
         <v>46051</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27419,7 +27419,7 @@
         <v>46051</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         <v>46178</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27565,7 +27565,7 @@
         <v>46178</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>46178</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27711,7 +27711,7 @@
         <v>45539</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27784,7 +27784,7 @@
         <v>45439</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27857,7 +27857,7 @@
         <v>46063</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27930,7 +27930,7 @@
         <v>46182</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45005</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28076,7 +28076,7 @@
         <v>44684</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>44593</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28222,7 +28222,7 @@
         <v>45544</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>44725</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         <v>46072</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28441,7 +28441,7 @@
         <v>45362</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28514,7 +28514,7 @@
         <v>44802</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28587,7 +28587,7 @@
         <v>46086</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         <v>46086</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28733,7 +28733,7 @@
         <v>46086</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>46086</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28879,7 +28879,7 @@
         <v>45050</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28952,7 +28952,7 @@
         <v>45572</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29025,7 +29025,7 @@
         <v>45450</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29103,7 +29103,7 @@
         <v>46185</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29176,7 +29176,7 @@
         <v>46185</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29249,7 +29249,7 @@
         <v>45377</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29322,7 +29322,7 @@
         <v>44866</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29400,7 +29400,7 @@
         <v>46092</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29473,7 +29473,7 @@
         <v>45722</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29546,7 +29546,7 @@
         <v>45547</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>46190</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>46099</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>46193</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>46191</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>46185</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45789</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45169</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30135,7 +30135,7 @@
         <v>46105</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>44699</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>45978</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30359,7 +30359,7 @@
         <v>45774</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>45334</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45035</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45035</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45377</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>46197</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>46197</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>44952</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45267</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45050</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>46111</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>44523</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45376</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>44511</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31391,7 +31391,7 @@
         <v>44511</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31464,7 +31464,7 @@
         <v>45363</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45097</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31615,7 +31615,7 @@
         <v>46199</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31688,7 +31688,7 @@
         <v>45210</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>44784</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>45196</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>46126</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>45392</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32053,7 +32053,7 @@
         <v>45392</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45888</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>45629</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45629</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45736</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32418,7 +32418,7 @@
         <v>45334</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>44679</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32564,7 +32564,7 @@
         <v>44851</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45568</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45762</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>45415</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>46203</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45716</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>45472</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>45227</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>45895</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>45391</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33299,7 +33299,7 @@
         <v>44866</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>45258</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33450,7 +33450,7 @@
         <v>46203</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33523,7 +33523,7 @@
         <v>44887</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33596,7 +33596,7 @@
         <v>44649</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33669,7 +33669,7 @@
         <v>44851</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>44622</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>44622</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33888,7 +33888,7 @@
         <v>45376</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33961,7 +33961,7 @@
         <v>45519</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34034,7 +34034,7 @@
         <v>45467</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34107,7 +34107,7 @@
         <v>45574</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>45575</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34253,7 +34253,7 @@
         <v>45258</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34326,7 +34326,7 @@
         <v>45096</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34399,7 +34399,7 @@
         <v>45035</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>44586</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34545,7 +34545,7 @@
         <v>45761</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34618,7 +34618,7 @@
         <v>45089</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34691,7 +34691,7 @@
         <v>45751</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>45751</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>45624</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34920,7 +34920,7 @@
         <v>45701</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34993,7 +34993,7 @@
         <v>45394</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35066,7 +35066,7 @@
         <v>45594</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>45070</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>46255</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35285,7 +35285,7 @@
         <v>45310</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>46213</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>45301</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>45595</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>46213</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35655,7 +35655,7 @@
         <v>46213</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35728,7 +35728,7 @@
         <v>45394</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35801,7 +35801,7 @@
         <v>45544</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>46213</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35952,7 +35952,7 @@
         <v>45044</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36025,7 +36025,7 @@
         <v>45474</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36098,7 +36098,7 @@
         <v>45747</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36171,7 +36171,7 @@
         <v>45747</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36244,7 +36244,7 @@
         <v>45747</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36317,7 +36317,7 @@
         <v>44831</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36390,7 +36390,7 @@
         <v>44831</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36463,7 +36463,7 @@
         <v>45317</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36536,7 +36536,7 @@
         <v>45075</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36609,7 +36609,7 @@
         <v>44882</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36682,7 +36682,7 @@
         <v>45075</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45625</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36828,7 +36828,7 @@
         <v>45070</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36901,7 +36901,7 @@
         <v>44547</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36974,7 +36974,7 @@
         <v>45259</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37047,7 +37047,7 @@
         <v>45609</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37120,7 +37120,7 @@
         <v>44587</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37193,7 +37193,7 @@
         <v>46265</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37266,7 +37266,7 @@
         <v>45313</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>45306</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37412,7 +37412,7 @@
         <v>45096</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45096</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37568,7 +37568,7 @@
         <v>45131</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37641,7 +37641,7 @@
         <v>46265</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>46265</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>46265</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37860,7 +37860,7 @@
         <v>46265</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37933,7 +37933,7 @@
         <v>45328</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38011,7 +38011,7 @@
         <v>45113</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38084,7 +38084,7 @@
         <v>46224</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38162,7 +38162,7 @@
         <v>46265</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38235,7 +38235,7 @@
         <v>46265</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>46265</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38381,7 +38381,7 @@
         <v>45301</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38454,7 +38454,7 @@
         <v>45672</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45266</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38600,7 +38600,7 @@
         <v>44665</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>45789</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38746,7 +38746,7 @@
         <v>45922</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38819,7 +38819,7 @@
         <v>45096</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38897,7 +38897,7 @@
         <v>46231</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45641</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39048,7 +39048,7 @@
         <v>45075</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>46277</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39194,7 +39194,7 @@
         <v>46280</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39267,7 +39267,7 @@
         <v>45616</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>46090</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39413,7 +39413,7 @@
         <v>46282</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39486,7 +39486,7 @@
         <v>46240</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39564,7 +39564,7 @@
         <v>45797</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39637,7 +39637,7 @@
         <v>46240</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39715,7 +39715,7 @@
         <v>45816</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>45814</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39861,7 +39861,7 @@
         <v>45816</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39934,7 +39934,7 @@
         <v>45815</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45820</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40080,7 +40080,7 @@
         <v>45820</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45819</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>45722</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>45737</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>45740</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>45747</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>45740</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40591,7 +40591,7 @@
         <v>45831</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40664,7 +40664,7 @@
         <v>45832</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40737,7 +40737,7 @@
         <v>45328</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45328</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45842</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40966,7 +40966,7 @@
         <v>45832</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45824</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41112,7 +41112,7 @@
         <v>45813</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>45848</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>45715</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45876</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41404,7 +41404,7 @@
         <v>45877</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41477,7 +41477,7 @@
         <v>45877</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41550,7 +41550,7 @@
         <v>45883</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41623,7 +41623,7 @@
         <v>45394</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45389</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41769,7 +41769,7 @@
         <v>44735</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41842,7 +41842,7 @@
         <v>45454</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41915,7 +41915,7 @@
         <v>45422</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41988,7 +41988,7 @@
         <v>44767</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42061,7 +42061,7 @@
         <v>45104</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>45104</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45385</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>45422</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42353,7 +42353,7 @@
         <v>45422</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42426,7 +42426,7 @@
         <v>44865</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42499,7 +42499,7 @@
         <v>44735</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42572,7 +42572,7 @@
         <v>44735</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42645,7 +42645,7 @@
         <v>45769</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45820</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42791,7 +42791,7 @@
         <v>45667</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>45677</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45638</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45685</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45881</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43156,7 +43156,7 @@
         <v>45740</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43229,7 +43229,7 @@
         <v>44866</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43302,7 +43302,7 @@
         <v>46049</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>46092</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>46092</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>46114</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43594,7 +43594,7 @@
         <v>45775</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43667,7 +43667,7 @@
         <v>46274</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>

--- a/Översikt TRANEMO.xlsx
+++ b/Översikt TRANEMO.xlsx
@@ -601,7 +601,7 @@
         <v>45523</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45132</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45450</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45087</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45917</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>44739</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>44658</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44770</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44767</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45377</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45397</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45484</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46072</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44732</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45621</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>44770</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44848</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>45392</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45800</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45906</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>45922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>45575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44609</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>46126</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45740</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45831</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45093</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44947</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45096</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>46244</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45328</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45608</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44706</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45422</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>45638</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45147</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44800</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44564</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44574</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>44585</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44472</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44487</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44599</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44851</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44734</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44670</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44494</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44804</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44583</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44616</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44502</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>44495</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44585</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44722</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44675</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44775</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44599</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44509</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44680</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44630</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44793</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44800</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44732</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44872</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44882</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44530</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44837</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44469</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44481</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44788</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44522</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>44500</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44705</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44735</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44599</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44552</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45211</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>45222</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45362</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>45415</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>44866</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45526</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44866</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>45224</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45359</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>45425</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44882</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45747</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45424</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>44838</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>44882</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>44882</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>44887</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44851</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>45463</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45463</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>44855</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>44866</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>45391</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>45317</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>45574</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44867</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>45467</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45257</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>45720</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>46013</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>46013</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>46013</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45714</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45714</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>45715</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>44947</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45695</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45705</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>45472</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44852</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>44583</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45467</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>45484</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45245</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45169</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45883</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45797</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44867</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45062</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45819</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45922</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45426</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45089</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>44523</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45894</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44511</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>45303</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>45897</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45897</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>44547</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45897</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>44593</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45362</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45075</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45743</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44988</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>45906</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45362</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>44652</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>45544</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>46051</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44665</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>46051</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45912</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45810</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45917</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45551</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44958</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45917</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>46063</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45359</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45922</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>46072</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>46086</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>46086</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>46086</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>46086</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>45933</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45439</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45595</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>45936</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45594</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45933</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45937</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45937</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45937</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>46092</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45679</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45679</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>45937</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45938</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45939</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>45939</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>45939</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>45939</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45939</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45544</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45399</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45897</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>46099</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45070</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45377</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45789</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45097</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45950</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45950</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45950</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45950</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45950</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45624</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45774</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>44665</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45629</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45629</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45266</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>46111</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45301</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>44965</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45363</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45376</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44699</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45966</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45625</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>46126</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>45362</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45131</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45978</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45978</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>45816</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>45978</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>45978</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>45978</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45978</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45980</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45174</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>44802</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>45813</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45701</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45762</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>45672</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45519</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45816</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45096</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45096</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45005</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45436</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45993</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45994</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45740</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45994</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45785</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45993</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45720</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>46000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45670</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45140</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45891</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>45814</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45815</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>45227</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45722</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45715</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>45467</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45895</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45035</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45825</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45819</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45820</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45820</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>46010</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45679</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>45714</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>45587</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44831</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>44831</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>46013</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45711</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>45688</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45093</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45740</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45762</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45070</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>44537</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45740</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>45747</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45251</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45740</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45722</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45737</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>44851</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44867</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45551</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>45035</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>45035</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>44522</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45831</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>45832</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44882</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45096</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45390</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45751</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>46160</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>46160</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>46160</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>44586</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45763</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45763</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>45328</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45328</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45196</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45842</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>45832</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45848</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45824</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45813</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45574</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44552</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45772</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45002</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45270</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45096</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>46174</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45424</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>45544</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45574</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45306</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45394</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>46176</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>46178</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>46178</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>46178</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>46182</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>46185</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45715</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45328</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45316</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45187</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>44544</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>45392</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>45392</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45334</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>46191</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>45394</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>46190</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>45876</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>46185</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>44656</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>45644</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>45734</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>46193</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>46197</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>45877</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45877</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45377</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45673</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>45701</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>46199</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>44622</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44622</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>46203</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>46203</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>45316</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>45316</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>45140</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>44958</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>45153</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45183</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44649</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>45888</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>45572</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45736</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>45747</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45747</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45716</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>45196</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>45673</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>45547</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45656</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44819</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44679</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>46213</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45096</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45096</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45096</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45713</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>46255</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>46213</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45701</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>45694</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>46213</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>46213</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>44720</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45572</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>44596</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45113</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>45258</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>45157</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>44799</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45169</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44748</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         <v>45761</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>44725</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45315</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>46265</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32360,7 +32360,7 @@
         <v>46265</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>46265</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45624</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>46265</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>46265</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>46265</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>45716</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>45315</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>46265</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>46265</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45210</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>45267</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45227</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>45301</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>46224</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>45740</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45922</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>45258</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>46231</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>44952</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>45747</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>45747</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45747</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45259</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45245</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>46277</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>45450</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>46280</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>46090</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45376</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>44904</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44732</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>45547</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>46282</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45566</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>44511</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>46240</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45316</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>46240</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>45789</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>44867</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>46105</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45568</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>44578</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44587</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>44593</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45566</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45188</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>45546</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>46289</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>46289</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>45301</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44600</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>44656</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>46289</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>46289</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44983</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>44866</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>45222</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>45363</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36800,7 +36800,7 @@
         <v>45978</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45079</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>46289</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>46289</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>45978</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>45050</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37248,7 +37248,7 @@
         <v>45425</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>44578</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45978</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>46289</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>44902</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44931</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>45722</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>45044</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>44684</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>44658</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45174</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45050</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38129,7 +38129,7 @@
         <v>44958</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>45075</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44977</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>44958</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>45034</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>44963</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>45310</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44998</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45609</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>45701</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45575</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45484</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44958</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45377</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45641</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45044</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>45329</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45099</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45170</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45259</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45664</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>45317</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45665</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45342</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44970</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>44749</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>44866</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>44784</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45474</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45539</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45321</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45392</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>45155</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45334</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45751</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45751</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40777,7 +40777,7 @@
         <v>45259</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>45313</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45227</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45315</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45327</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45315</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45096</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>45075</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45641</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45616</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45394</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>44735</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44735</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>44735</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45389</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45454</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>45422</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>44767</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>45104</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45104</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45385</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>45422</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45422</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44865</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45769</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>45820</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42680,7 +42680,7 @@
         <v>45667</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>45677</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45638</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45685</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45881</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45740</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44866</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>46049</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>46092</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>46092</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>46114</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45775</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>46274</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>

--- a/Översikt TRANEMO.xlsx
+++ b/Översikt TRANEMO.xlsx
@@ -601,7 +601,7 @@
         <v>45523</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45132</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45450</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45087</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45917</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>44739</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>44658</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44770</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44767</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45377</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45397</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45484</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46072</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44732</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>45621</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>44770</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>44848</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>45392</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45800</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>45906</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         <v>45922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3751,7 +3751,7 @@
         <v>45575</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44609</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3975,7 +3975,7 @@
         <v>46126</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4080,7 +4080,7 @@
         <v>45740</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>45831</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45093</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4404,7 +4404,7 @@
         <v>44947</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>45096</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>44644</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>46244</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45328</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45608</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44866</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44706</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45422</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>45638</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45147</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44800</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44564</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44574</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>44585</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44472</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44487</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44599</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44851</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44734</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44670</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44494</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44804</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44583</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44616</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44502</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>44495</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>44585</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44722</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44675</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44775</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44599</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44509</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44680</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44630</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44793</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44800</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44732</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44872</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44882</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44530</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44837</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44469</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44481</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44788</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44522</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>44500</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44705</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44735</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44599</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44552</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>45211</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9303,7 +9303,7 @@
         <v>45222</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9376,7 +9376,7 @@
         <v>45362</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9449,7 +9449,7 @@
         <v>45415</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
         <v>44866</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45526</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>44866</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9751,7 +9751,7 @@
         <v>45224</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>45359</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9902,7 +9902,7 @@
         <v>45425</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44882</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>45747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>45747</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10194,7 +10194,7 @@
         <v>45424</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10267,7 +10267,7 @@
         <v>44838</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>44882</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>44882</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>44887</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44851</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>45463</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>45463</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>44855</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>44866</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>45391</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11002,7 +11002,7 @@
         <v>45317</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11075,7 +11075,7 @@
         <v>45574</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44867</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11226,7 +11226,7 @@
         <v>45467</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11299,7 +11299,7 @@
         <v>45257</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11372,7 +11372,7 @@
         <v>45720</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11445,7 +11445,7 @@
         <v>46013</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11518,7 +11518,7 @@
         <v>46013</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11591,7 +11591,7 @@
         <v>46013</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45714</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>45714</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11810,7 +11810,7 @@
         <v>45715</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>44947</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11956,7 +11956,7 @@
         <v>45695</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45705</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12102,7 +12102,7 @@
         <v>45472</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12175,7 +12175,7 @@
         <v>44852</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12248,7 +12248,7 @@
         <v>44583</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12321,7 +12321,7 @@
         <v>45467</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12394,7 +12394,7 @@
         <v>45484</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12467,7 +12467,7 @@
         <v>45245</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12540,7 +12540,7 @@
         <v>45169</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12613,7 +12613,7 @@
         <v>45883</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
         <v>45797</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12759,7 +12759,7 @@
         <v>44867</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12832,7 +12832,7 @@
         <v>45062</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45819</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45922</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45426</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45089</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>44523</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45894</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>44511</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>45303</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>45897</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>45897</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>44547</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13718,7 +13718,7 @@
         <v>45897</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>44593</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45362</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45075</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45743</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>44988</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>45906</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45362</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14312,7 +14312,7 @@
         <v>44652</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14385,7 +14385,7 @@
         <v>45544</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14458,7 +14458,7 @@
         <v>46051</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44665</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14604,7 +14604,7 @@
         <v>46051</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>45912</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14750,7 +14750,7 @@
         <v>45810</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45917</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45551</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44958</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45917</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>46063</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45359</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45922</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>46072</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>46086</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>46086</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>46086</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>46086</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>45933</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45439</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45595</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>45936</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45594</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45933</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45937</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45937</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45937</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>46092</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45679</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45679</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>45937</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16653,7 +16653,7 @@
         <v>45938</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>45939</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>45939</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>45939</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16945,7 +16945,7 @@
         <v>45939</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45939</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>45544</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45399</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17237,7 +17237,7 @@
         <v>45897</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>46099</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>45070</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45377</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>45789</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45097</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45950</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45950</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45950</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
         <v>45950</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17972,7 +17972,7 @@
         <v>45950</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45624</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45774</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>44665</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45629</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45629</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45266</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>46111</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45301</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>44965</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45363</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45376</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18863,7 +18863,7 @@
         <v>44699</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>45966</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45625</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>46126</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>45362</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45131</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45978</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45978</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>45816</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19520,7 +19520,7 @@
         <v>45978</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>45978</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>45978</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45978</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45980</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>45174</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19958,7 +19958,7 @@
         <v>44802</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20031,7 +20031,7 @@
         <v>45813</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45701</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20177,7 +20177,7 @@
         <v>45762</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20250,7 +20250,7 @@
         <v>45672</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20323,7 +20323,7 @@
         <v>45519</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>45816</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20469,7 +20469,7 @@
         <v>45096</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
         <v>45096</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20615,7 +20615,7 @@
         <v>45005</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20688,7 +20688,7 @@
         <v>45436</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>45993</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45994</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20907,7 +20907,7 @@
         <v>45740</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20980,7 +20980,7 @@
         <v>45994</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21053,7 +21053,7 @@
         <v>45785</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21126,7 +21126,7 @@
         <v>45993</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>45720</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21272,7 +21272,7 @@
         <v>46000</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21345,7 +21345,7 @@
         <v>45670</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21418,7 +21418,7 @@
         <v>45140</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21491,7 +21491,7 @@
         <v>45891</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>45814</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21637,7 +21637,7 @@
         <v>45815</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21710,7 +21710,7 @@
         <v>45227</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45722</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45715</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21929,7 +21929,7 @@
         <v>45467</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22002,7 +22002,7 @@
         <v>45895</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22075,7 +22075,7 @@
         <v>45035</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22148,7 +22148,7 @@
         <v>45825</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22221,7 +22221,7 @@
         <v>45819</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22294,7 +22294,7 @@
         <v>45820</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45820</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22440,7 +22440,7 @@
         <v>46010</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22513,7 +22513,7 @@
         <v>45679</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22586,7 +22586,7 @@
         <v>45714</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>45587</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22732,7 +22732,7 @@
         <v>44831</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>44831</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22878,7 +22878,7 @@
         <v>46013</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22951,7 +22951,7 @@
         <v>45711</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23024,7 +23024,7 @@
         <v>45688</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23097,7 +23097,7 @@
         <v>45093</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23170,7 +23170,7 @@
         <v>45740</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23243,7 +23243,7 @@
         <v>45762</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23316,7 +23316,7 @@
         <v>45070</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23389,7 +23389,7 @@
         <v>44537</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>45740</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23535,7 +23535,7 @@
         <v>45747</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23608,7 +23608,7 @@
         <v>45251</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23681,7 +23681,7 @@
         <v>45740</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23754,7 +23754,7 @@
         <v>45722</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23827,7 +23827,7 @@
         <v>45737</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23900,7 +23900,7 @@
         <v>44851</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>44867</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24046,7 +24046,7 @@
         <v>45551</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24119,7 +24119,7 @@
         <v>45035</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24192,7 +24192,7 @@
         <v>45035</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>44522</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24338,7 +24338,7 @@
         <v>45831</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24411,7 +24411,7 @@
         <v>45832</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>44882</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24557,7 +24557,7 @@
         <v>45096</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>45390</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24708,7 +24708,7 @@
         <v>45751</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>46160</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>46160</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24932,7 +24932,7 @@
         <v>46160</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25005,7 +25005,7 @@
         <v>44586</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25078,7 +25078,7 @@
         <v>45763</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>45763</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25224,7 +25224,7 @@
         <v>45328</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25302,7 +25302,7 @@
         <v>45328</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45196</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25453,7 +25453,7 @@
         <v>45842</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>45832</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45848</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>45824</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25745,7 +25745,7 @@
         <v>45813</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>45574</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25891,7 +25891,7 @@
         <v>44552</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25964,7 +25964,7 @@
         <v>45772</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26037,7 +26037,7 @@
         <v>45002</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>45270</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45096</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26256,7 +26256,7 @@
         <v>46174</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26329,7 +26329,7 @@
         <v>45424</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26402,7 +26402,7 @@
         <v>45544</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26480,7 +26480,7 @@
         <v>45574</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45306</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26626,7 +26626,7 @@
         <v>45394</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26699,7 +26699,7 @@
         <v>46176</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>46178</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>46178</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26918,7 +26918,7 @@
         <v>46178</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>46182</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>46185</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27137,7 +27137,7 @@
         <v>45715</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27210,7 +27210,7 @@
         <v>45328</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45316</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45187</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>44544</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>45392</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>45392</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45334</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>46191</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>45394</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27872,7 +27872,7 @@
         <v>46190</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>45876</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         <v>46185</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28091,7 +28091,7 @@
         <v>44656</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28164,7 +28164,7 @@
         <v>45644</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28237,7 +28237,7 @@
         <v>45734</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>46193</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>46197</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>45877</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>45877</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         <v>45377</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45673</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28748,7 +28748,7 @@
         <v>45701</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28821,7 +28821,7 @@
         <v>46199</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28894,7 +28894,7 @@
         <v>44622</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28967,7 +28967,7 @@
         <v>44622</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29040,7 +29040,7 @@
         <v>46203</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29113,7 +29113,7 @@
         <v>46203</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>45316</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29259,7 +29259,7 @@
         <v>45316</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29332,7 +29332,7 @@
         <v>45140</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>44958</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29478,7 +29478,7 @@
         <v>45153</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29551,7 +29551,7 @@
         <v>45183</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>44649</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29697,7 +29697,7 @@
         <v>45888</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29770,7 +29770,7 @@
         <v>45572</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29843,7 +29843,7 @@
         <v>45736</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>45747</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45747</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30062,7 +30062,7 @@
         <v>45716</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30140,7 +30140,7 @@
         <v>45196</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30213,7 +30213,7 @@
         <v>45673</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30286,7 +30286,7 @@
         <v>45547</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>45656</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44819</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>44679</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>46213</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45096</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>45096</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30812,7 +30812,7 @@
         <v>45096</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>45713</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30958,7 +30958,7 @@
         <v>46255</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31031,7 +31031,7 @@
         <v>46213</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31104,7 +31104,7 @@
         <v>45701</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31177,7 +31177,7 @@
         <v>45694</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31255,7 +31255,7 @@
         <v>46213</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31328,7 +31328,7 @@
         <v>46213</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31401,7 +31401,7 @@
         <v>44720</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45572</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>44596</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45113</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31698,7 +31698,7 @@
         <v>45258</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31771,7 +31771,7 @@
         <v>45157</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>44799</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45169</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31990,7 +31990,7 @@
         <v>44748</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32068,7 +32068,7 @@
         <v>45761</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32141,7 +32141,7 @@
         <v>44725</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32214,7 +32214,7 @@
         <v>45315</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32287,7 +32287,7 @@
         <v>46265</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32360,7 +32360,7 @@
         <v>46265</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32433,7 +32433,7 @@
         <v>46265</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32506,7 +32506,7 @@
         <v>45624</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32579,7 +32579,7 @@
         <v>46265</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>46265</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32725,7 +32725,7 @@
         <v>46265</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32798,7 +32798,7 @@
         <v>45716</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32871,7 +32871,7 @@
         <v>45315</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32944,7 +32944,7 @@
         <v>46265</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>46265</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33090,7 +33090,7 @@
         <v>45210</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33163,7 +33163,7 @@
         <v>45267</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33236,7 +33236,7 @@
         <v>45227</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33309,7 +33309,7 @@
         <v>45301</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>46224</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>45740</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>45922</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>45258</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33679,7 +33679,7 @@
         <v>46231</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>44952</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>45747</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>45747</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33976,7 +33976,7 @@
         <v>45747</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45259</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>45245</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>46277</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>45450</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>46280</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>46090</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45376</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34565,7 +34565,7 @@
         <v>44904</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>44732</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34711,7 +34711,7 @@
         <v>45547</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34789,7 +34789,7 @@
         <v>46282</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34862,7 +34862,7 @@
         <v>45566</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         <v>44511</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35008,7 +35008,7 @@
         <v>46240</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35086,7 +35086,7 @@
         <v>45316</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35159,7 +35159,7 @@
         <v>46240</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35237,7 +35237,7 @@
         <v>45789</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35310,7 +35310,7 @@
         <v>44867</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35383,7 +35383,7 @@
         <v>46105</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35461,7 +35461,7 @@
         <v>45568</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35534,7 +35534,7 @@
         <v>44578</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35607,7 +35607,7 @@
         <v>44587</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35680,7 +35680,7 @@
         <v>44593</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45566</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35826,7 +35826,7 @@
         <v>45188</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35899,7 +35899,7 @@
         <v>45546</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35972,7 +35972,7 @@
         <v>46289</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36050,7 +36050,7 @@
         <v>46289</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>45301</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44600</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>44656</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36347,7 +36347,7 @@
         <v>46289</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>46289</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36503,7 +36503,7 @@
         <v>44983</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>44866</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36654,7 +36654,7 @@
         <v>45222</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>45363</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36800,7 +36800,7 @@
         <v>45978</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36873,7 +36873,7 @@
         <v>45079</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>46289</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>46289</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37102,7 +37102,7 @@
         <v>45978</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>45050</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37248,7 +37248,7 @@
         <v>45425</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>44578</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45978</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>46289</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37545,7 +37545,7 @@
         <v>44902</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44931</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>45722</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>45044</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>44684</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37910,7 +37910,7 @@
         <v>44658</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37983,7 +37983,7 @@
         <v>45174</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45050</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38129,7 +38129,7 @@
         <v>44958</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38202,7 +38202,7 @@
         <v>45075</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>44977</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>44958</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38421,7 +38421,7 @@
         <v>45034</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>44963</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38567,7 +38567,7 @@
         <v>45310</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38645,7 +38645,7 @@
         <v>44998</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38718,7 +38718,7 @@
         <v>45609</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>45701</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45575</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45484</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>44958</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39083,7 +39083,7 @@
         <v>45377</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39156,7 +39156,7 @@
         <v>45641</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45044</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>45329</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45099</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45170</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45259</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45664</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>45317</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>45665</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45342</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>44970</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>44749</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>44866</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40110,7 +40110,7 @@
         <v>44784</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45474</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45539</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40329,7 +40329,7 @@
         <v>45321</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40402,7 +40402,7 @@
         <v>45392</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40475,7 +40475,7 @@
         <v>45155</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40548,7 +40548,7 @@
         <v>45334</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40621,7 +40621,7 @@
         <v>45751</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40699,7 +40699,7 @@
         <v>45751</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40777,7 +40777,7 @@
         <v>45259</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40850,7 +40850,7 @@
         <v>45313</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
         <v>45227</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45315</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45327</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45315</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45096</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41293,7 +41293,7 @@
         <v>45075</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41366,7 +41366,7 @@
         <v>45641</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45616</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45394</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>44735</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>44735</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>44735</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45389</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45454</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>45422</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>44767</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>45104</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45104</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45385</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>45422</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>45422</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44865</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>45769</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>45820</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42680,7 +42680,7 @@
         <v>45667</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>45677</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45638</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45685</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45881</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45740</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>44866</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>46049</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>46092</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>46092</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>46114</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45775</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>46274</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>

--- a/Översikt TRANEMO.xlsx
+++ b/Översikt TRANEMO.xlsx
@@ -601,7 +601,7 @@
         <v>45523</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45132</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45450</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45087</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45917</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>44770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44739</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44767</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>44658</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45377</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>45397</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46072</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44770</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>44732</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45621</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>44609</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45906</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45800</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44848</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45740</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>46126</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>45831</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45575</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44866</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45392</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>44947</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>45096</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>46244</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45328</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>45093</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45422</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>44706</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44706</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>45638</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45147</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44800</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44564</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>44585</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44472</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44487</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44599</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44734</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44851</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44670</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44494</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44804</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44616</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44583</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44502</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>44585</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44495</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44675</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44722</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44775</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44599</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44509</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44680</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44799</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44630</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44793</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44800</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44732</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44872</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44882</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44530</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44837</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44481</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44522</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44500</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44788</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>44735</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44705</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44599</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44552</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44593</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44596</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45362</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>44998</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>45316</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45315</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>45196</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44656</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>45270</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44732</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>45157</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45641</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>44882</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45747</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>45747</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>45713</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>45377</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>45616</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>45315</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>44947</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>45484</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>45819</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>44958</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>45327</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>44852</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>45183</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>45551</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>45740</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>46010</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>46013</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>46013</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>46013</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>46013</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>45363</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>45714</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>45705</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>45720</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>45695</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>45711</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>45688</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45715</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>45714</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45153</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44902</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>45566</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44867</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44931</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>45894</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>45897</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>45897</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45897</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>45743</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>45701</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>45922</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>45574</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45426</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>45259</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>45224</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>45906</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45810</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45301</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45572</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45912</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45797</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45257</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45917</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>45917</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>46051</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>46051</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>44958</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45922</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45694</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44866</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45467</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45093</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45044</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45933</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45933</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44988</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45251</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>46063</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45936</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45937</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45937</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45937</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>44799</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45227</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>45939</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45939</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45937</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>44537</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45939</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45939</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45938</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>44867</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45897</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>46072</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45751</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45763</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45222</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45317</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>44983</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45763</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45950</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45950</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>45099</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45950</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45950</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45950</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45544</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>46086</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>46086</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>46086</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>46086</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45816</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45174</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>44583</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>46092</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45747</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45747</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45814</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45734</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45566</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45816</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>45096</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45966</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>46099</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45789</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>45815</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>45978</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>45978</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>45978</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>45079</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45978</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>45978</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>45978</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>45774</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>45980</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>45316</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>45820</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45820</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45259</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>46111</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45819</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45245</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45376</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45363</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45993</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>45993</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45222</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45722</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45737</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>44855</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44904</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45740</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>44578</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45994</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>45994</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>46126</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45747</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45740</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>46000</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>45701</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44819</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45831</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44544</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45832</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>45399</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>45425</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>45762</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>45328</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45328</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45362</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45895</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45715</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45467</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45673</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45891</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>44748</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45436</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45813</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45716</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>45832</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>45824</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>44749</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45587</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45813</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>45848</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45762</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>45785</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>45359</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>45714</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>45547</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45321</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45425</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45096</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45096</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>44867</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45169</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45679</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45825</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45740</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45740</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45227</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45670</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45720</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45484</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44977</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45644</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45211</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45315</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45315</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44963</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45329</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44522</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45715</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44866</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44838</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44958</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45390</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>44578</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>45546</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45359</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45342</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>45034</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45174</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>46160</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>46160</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>46160</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45876</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45877</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45877</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45772</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44958</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45722</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44658</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45624</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>44970</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45883</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46174</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45096</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>46176</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45187</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45140</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>46178</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>46178</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45245</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>46178</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45062</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45392</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45679</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45679</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45424</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45424</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>46182</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>44866</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>45303</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45170</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44965</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28393,7 +28393,7 @@
         <v>44552</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>46185</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>44720</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44882</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>44652</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>46190</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44882</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>46193</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>46191</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45551</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>45316</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>46185</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45701</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>44665</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45656</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45188</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>45574</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>46197</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>44867</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>45140</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>46199</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>45888</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>45463</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>45463</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>46203</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>46203</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45665</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44656</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44600</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45526</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45316</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45664</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>46213</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>46213</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>46213</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45673</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45002</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>46213</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>46265</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>46265</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>46265</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45539</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45439</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>46265</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>46265</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>45005</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44684</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>44593</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>46224</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>46265</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>46265</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>46265</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45544</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>44725</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45362</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>45922</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>44802</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>46231</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45050</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>46277</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>46280</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>45572</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45450</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>46090</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>45377</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>46282</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44866</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>46240</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45722</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>45547</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>46240</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45169</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44699</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45789</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>46105</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45334</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>45035</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45035</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>45377</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>44952</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45267</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>45050</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44523</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>46289</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>46289</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>46289</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>46289</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>46289</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>44511</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44511</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>46289</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>46289</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>45097</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>45210</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>44784</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45978</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>45196</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>45978</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>45978</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45392</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45392</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45629</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>45629</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45736</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45334</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>44679</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>46294</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44851</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>45568</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45415</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36498,7 +36498,7 @@
         <v>45716</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>46294</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>45472</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45227</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45391</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>44866</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45258</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>44887</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>44649</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>44851</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44622</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>44622</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>45376</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45362</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>45519</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45842</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>45467</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45574</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45575</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>46255</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45258</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>45096</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>45035</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>44586</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45761</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>45089</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45751</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45751</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>45624</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45701</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>45394</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38781,7 +38781,7 @@
         <v>45594</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>45070</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45310</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45301</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45595</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45394</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>45544</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>45044</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45474</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45747</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45747</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45747</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>44831</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>44831</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45317</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45075</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>44882</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>45075</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45625</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45070</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>44547</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45259</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45609</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44587</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45313</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45306</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>45096</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45096</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>45131</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45328</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45113</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45301</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45672</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45266</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>44665</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45096</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45641</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45075</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>45394</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>45389</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>44735</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45454</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45422</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>44767</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45104</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>45104</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45385</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45422</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>45422</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44865</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44735</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>44735</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>45769</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42680,7 +42680,7 @@
         <v>45820</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>45667</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45677</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45638</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45685</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45881</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>45740</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>44866</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>46049</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>46092</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>46092</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>46114</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45775</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>46274</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>

--- a/Översikt TRANEMO.xlsx
+++ b/Översikt TRANEMO.xlsx
@@ -601,7 +601,7 @@
         <v>45523</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45132</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45450</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45087</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45917</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>44770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44739</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44767</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>44658</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45377</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>45397</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>46072</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2542,7 +2542,7 @@
         <v>44770</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2652,7 +2652,7 @@
         <v>44732</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45621</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44474</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>44609</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45906</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>45800</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44848</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>45740</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>46126</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>45831</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>45575</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>44866</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44644</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>45392</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>44947</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4719,7 +4719,7 @@
         <v>45096</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>46244</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4934,7 +4934,7 @@
         <v>45328</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>45093</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>45422</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>44706</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>44706</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5481,7 +5481,7 @@
         <v>45638</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>45147</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5691,7 +5691,7 @@
         <v>44800</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5910,7 +5910,7 @@
         <v>44564</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>44585</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6061,7 +6061,7 @@
         <v>44472</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>44637</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6207,7 +6207,7 @@
         <v>44487</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6280,7 +6280,7 @@
         <v>44852</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44599</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6431,7 +6431,7 @@
         <v>44734</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44851</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6577,7 +6577,7 @@
         <v>44670</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>44494</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6728,7 +6728,7 @@
         <v>44804</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6801,7 +6801,7 @@
         <v>44530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44616</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
         <v>44583</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>44887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44502</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>44585</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44495</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>44537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>44589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>44675</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         <v>44722</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7619,7 +7619,7 @@
         <v>44775</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>44599</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44509</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7838,7 +7838,7 @@
         <v>44680</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7911,7 +7911,7 @@
         <v>44799</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7984,7 +7984,7 @@
         <v>44630</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8057,7 +8057,7 @@
         <v>44793</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44800</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8203,7 +8203,7 @@
         <v>44732</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44872</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8354,7 +8354,7 @@
         <v>44882</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8427,7 +8427,7 @@
         <v>44530</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>44837</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44481</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8646,7 +8646,7 @@
         <v>44522</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8719,7 +8719,7 @@
         <v>44500</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8792,7 +8792,7 @@
         <v>44788</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>44735</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44705</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9011,7 +9011,7 @@
         <v>44599</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44552</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9157,7 +9157,7 @@
         <v>44593</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9230,7 +9230,7 @@
         <v>44596</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9308,7 +9308,7 @@
         <v>44958</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9381,7 +9381,7 @@
         <v>45362</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         <v>44998</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9527,7 +9527,7 @@
         <v>45316</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>45315</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9673,7 +9673,7 @@
         <v>45196</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44656</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>45270</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44732</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>45157</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45641</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>44882</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10184,7 +10184,7 @@
         <v>45747</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10257,7 +10257,7 @@
         <v>45747</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>45713</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10403,7 +10403,7 @@
         <v>45377</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10476,7 +10476,7 @@
         <v>45616</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10549,7 +10549,7 @@
         <v>45315</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10622,7 +10622,7 @@
         <v>44947</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>45484</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>45819</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>44958</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>45327</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10987,7 +10987,7 @@
         <v>44852</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11060,7 +11060,7 @@
         <v>45183</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11133,7 +11133,7 @@
         <v>45551</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>45740</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>46010</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>46013</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>46013</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11498,7 +11498,7 @@
         <v>46013</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>46013</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11644,7 +11644,7 @@
         <v>45363</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11717,7 +11717,7 @@
         <v>45714</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>45705</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>45720</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11936,7 +11936,7 @@
         <v>45695</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>45711</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>45688</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45715</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>45714</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>45153</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44902</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>45566</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44867</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44931</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>45894</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>45897</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>45897</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12895,7 +12895,7 @@
         <v>45897</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>45743</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13046,7 +13046,7 @@
         <v>45701</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>45922</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>45574</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>45426</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>45259</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>45224</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13494,7 +13494,7 @@
         <v>45906</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>45810</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13650,7 +13650,7 @@
         <v>45301</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45572</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45912</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>45797</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13942,7 +13942,7 @@
         <v>45257</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>45917</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14088,7 +14088,7 @@
         <v>45917</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>46051</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>46051</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14307,7 +14307,7 @@
         <v>44958</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14380,7 +14380,7 @@
         <v>45922</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14453,7 +14453,7 @@
         <v>45694</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14531,7 +14531,7 @@
         <v>44866</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14609,7 +14609,7 @@
         <v>45467</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14682,7 +14682,7 @@
         <v>45093</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45044</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>45933</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14901,7 +14901,7 @@
         <v>45933</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14974,7 +14974,7 @@
         <v>44988</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>45251</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>46063</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15193,7 +15193,7 @@
         <v>45936</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45937</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45937</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
         <v>45937</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15485,7 +15485,7 @@
         <v>45939</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15558,7 +15558,7 @@
         <v>44799</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>45227</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15704,7 +15704,7 @@
         <v>45939</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15777,7 +15777,7 @@
         <v>45939</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45937</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15923,7 +15923,7 @@
         <v>44537</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15996,7 +15996,7 @@
         <v>45939</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45939</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45938</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>44867</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>45897</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>46072</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>45751</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16517,7 +16517,7 @@
         <v>45763</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>45155</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>45222</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45317</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>44983</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45763</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16955,7 +16955,7 @@
         <v>45950</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17028,7 +17028,7 @@
         <v>45950</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17101,7 +17101,7 @@
         <v>45099</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>45950</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45950</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45950</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>45544</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17466,7 +17466,7 @@
         <v>46086</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>46086</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17612,7 +17612,7 @@
         <v>46086</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>46086</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17758,7 +17758,7 @@
         <v>45816</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45174</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>44583</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>46092</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>45747</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45747</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>45814</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45734</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18342,7 +18342,7 @@
         <v>45566</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18415,7 +18415,7 @@
         <v>45816</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18488,7 +18488,7 @@
         <v>45096</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18561,7 +18561,7 @@
         <v>45966</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>46099</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45789</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>45815</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>45978</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>45978</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>45978</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19072,7 +19072,7 @@
         <v>45079</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19145,7 +19145,7 @@
         <v>45978</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19218,7 +19218,7 @@
         <v>45978</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>45978</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>45774</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>45980</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>45316</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>45820</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19661,7 +19661,7 @@
         <v>45820</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45259</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>46111</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19880,7 +19880,7 @@
         <v>45819</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19953,7 +19953,7 @@
         <v>45245</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20026,7 +20026,7 @@
         <v>45376</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45363</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20182,7 +20182,7 @@
         <v>45993</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20255,7 +20255,7 @@
         <v>45993</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20328,7 +20328,7 @@
         <v>45222</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20401,7 +20401,7 @@
         <v>45722</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20474,7 +20474,7 @@
         <v>45737</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20547,7 +20547,7 @@
         <v>44855</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44904</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20693,7 +20693,7 @@
         <v>45740</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20766,7 +20766,7 @@
         <v>44578</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20839,7 +20839,7 @@
         <v>45994</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>45994</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20985,7 +20985,7 @@
         <v>46126</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21058,7 +21058,7 @@
         <v>45747</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>45740</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21204,7 +21204,7 @@
         <v>46000</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21277,7 +21277,7 @@
         <v>45701</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>44819</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21423,7 +21423,7 @@
         <v>45831</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
         <v>44544</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45832</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>45399</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
         <v>45425</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21788,7 +21788,7 @@
         <v>45762</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>45328</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21939,7 +21939,7 @@
         <v>45328</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22017,7 +22017,7 @@
         <v>45362</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22090,7 +22090,7 @@
         <v>45895</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22163,7 +22163,7 @@
         <v>45715</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22236,7 +22236,7 @@
         <v>45467</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45673</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45891</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>44748</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22533,7 +22533,7 @@
         <v>45436</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22606,7 +22606,7 @@
         <v>45813</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45716</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>45832</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>45824</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>44749</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45587</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23044,7 +23044,7 @@
         <v>45813</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23117,7 +23117,7 @@
         <v>45848</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45762</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23263,7 +23263,7 @@
         <v>45785</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23336,7 +23336,7 @@
         <v>45359</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23409,7 +23409,7 @@
         <v>45714</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23482,7 +23482,7 @@
         <v>45547</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23560,7 +23560,7 @@
         <v>45321</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>45425</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23706,7 +23706,7 @@
         <v>45096</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23779,7 +23779,7 @@
         <v>45096</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23852,7 +23852,7 @@
         <v>44867</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23925,7 +23925,7 @@
         <v>45169</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23998,7 +23998,7 @@
         <v>45679</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45825</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24144,7 +24144,7 @@
         <v>45740</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24217,7 +24217,7 @@
         <v>45740</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24290,7 +24290,7 @@
         <v>45227</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24363,7 +24363,7 @@
         <v>45670</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>45720</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45484</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24582,7 +24582,7 @@
         <v>44977</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24655,7 +24655,7 @@
         <v>45644</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24728,7 +24728,7 @@
         <v>45211</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24801,7 +24801,7 @@
         <v>45315</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24874,7 +24874,7 @@
         <v>45315</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24947,7 +24947,7 @@
         <v>44963</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25020,7 +25020,7 @@
         <v>45329</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>44522</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45715</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>44866</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25317,7 +25317,7 @@
         <v>44838</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25390,7 +25390,7 @@
         <v>44958</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25463,7 +25463,7 @@
         <v>45390</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25541,7 +25541,7 @@
         <v>44578</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>45546</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25687,7 +25687,7 @@
         <v>45359</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>45342</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25833,7 +25833,7 @@
         <v>45034</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25906,7 +25906,7 @@
         <v>45174</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25979,7 +25979,7 @@
         <v>46160</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>46160</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>46160</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>45876</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>45877</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>45877</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45772</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>44958</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26563,7 +26563,7 @@
         <v>45722</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26636,7 +26636,7 @@
         <v>44658</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26709,7 +26709,7 @@
         <v>45624</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26782,7 +26782,7 @@
         <v>44970</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45883</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         <v>46174</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>45096</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27074,7 +27074,7 @@
         <v>46176</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27147,7 +27147,7 @@
         <v>45187</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27220,7 +27220,7 @@
         <v>45140</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>46178</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>46178</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27439,7 +27439,7 @@
         <v>45245</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>46178</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45062</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27658,7 +27658,7 @@
         <v>45392</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27731,7 +27731,7 @@
         <v>45679</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>45679</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45424</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45424</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>46182</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>44866</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28174,7 +28174,7 @@
         <v>45303</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28247,7 +28247,7 @@
         <v>45170</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28320,7 +28320,7 @@
         <v>44965</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28393,7 +28393,7 @@
         <v>44552</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>46185</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28539,7 +28539,7 @@
         <v>44720</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28612,7 +28612,7 @@
         <v>44882</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>44652</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>46190</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28831,7 +28831,7 @@
         <v>44882</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28904,7 +28904,7 @@
         <v>46193</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28977,7 +28977,7 @@
         <v>46191</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29050,7 +29050,7 @@
         <v>45551</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         <v>45316</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29196,7 +29196,7 @@
         <v>46185</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45701</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29342,7 +29342,7 @@
         <v>44665</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45656</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45188</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29561,7 +29561,7 @@
         <v>45574</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29634,7 +29634,7 @@
         <v>46197</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29707,7 +29707,7 @@
         <v>44867</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29780,7 +29780,7 @@
         <v>45140</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29853,7 +29853,7 @@
         <v>46199</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>45888</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29999,7 +29999,7 @@
         <v>45463</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>45463</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30145,7 +30145,7 @@
         <v>46203</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>46203</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30291,7 +30291,7 @@
         <v>45665</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44656</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30437,7 +30437,7 @@
         <v>44600</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30510,7 +30510,7 @@
         <v>45526</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>45316</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>45664</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30729,7 +30729,7 @@
         <v>46213</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30802,7 +30802,7 @@
         <v>46213</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>46213</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30948,7 +30948,7 @@
         <v>45673</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45002</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31094,7 +31094,7 @@
         <v>46213</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31167,7 +31167,7 @@
         <v>46265</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>46265</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31313,7 +31313,7 @@
         <v>46265</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45539</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31459,7 +31459,7 @@
         <v>45439</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31532,7 +31532,7 @@
         <v>46265</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>46265</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>45005</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         <v>44684</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31824,7 +31824,7 @@
         <v>44593</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>46224</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31975,7 +31975,7 @@
         <v>46265</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32048,7 +32048,7 @@
         <v>46265</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32121,7 +32121,7 @@
         <v>46265</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45544</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v>44725</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32340,7 +32340,7 @@
         <v>45362</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32413,7 +32413,7 @@
         <v>45922</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32486,7 +32486,7 @@
         <v>44802</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32559,7 +32559,7 @@
         <v>46231</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32637,7 +32637,7 @@
         <v>45050</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>46277</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32783,7 +32783,7 @@
         <v>46280</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32856,7 +32856,7 @@
         <v>45572</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45450</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33007,7 +33007,7 @@
         <v>46090</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33080,7 +33080,7 @@
         <v>45377</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33153,7 +33153,7 @@
         <v>46282</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>44866</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>46240</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45722</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>45547</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33533,7 +33533,7 @@
         <v>46240</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33611,7 +33611,7 @@
         <v>45169</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44699</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45789</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>46105</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33908,7 +33908,7 @@
         <v>45334</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33981,7 +33981,7 @@
         <v>45035</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34054,7 +34054,7 @@
         <v>45035</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34127,7 +34127,7 @@
         <v>45377</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>44952</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34273,7 +34273,7 @@
         <v>45267</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34346,7 +34346,7 @@
         <v>45050</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34419,7 +34419,7 @@
         <v>44523</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>46289</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>46289</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>46289</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>46289</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>46289</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>44511</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>44511</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>46289</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35106,7 +35106,7 @@
         <v>46289</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35184,7 +35184,7 @@
         <v>45097</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35257,7 +35257,7 @@
         <v>45210</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>44784</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35403,7 +35403,7 @@
         <v>45978</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35476,7 +35476,7 @@
         <v>45196</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>45978</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>45978</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45392</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45392</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>45629</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35914,7 +35914,7 @@
         <v>45629</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35987,7 +35987,7 @@
         <v>45736</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36060,7 +36060,7 @@
         <v>45334</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>44679</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36206,7 +36206,7 @@
         <v>46294</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36279,7 +36279,7 @@
         <v>44851</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36352,7 +36352,7 @@
         <v>45568</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45415</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36498,7 +36498,7 @@
         <v>45716</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36576,7 +36576,7 @@
         <v>46294</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36649,7 +36649,7 @@
         <v>45472</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36722,7 +36722,7 @@
         <v>45227</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36795,7 +36795,7 @@
         <v>45391</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36868,7 +36868,7 @@
         <v>44866</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36946,7 +36946,7 @@
         <v>45258</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37019,7 +37019,7 @@
         <v>44887</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37092,7 +37092,7 @@
         <v>44649</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>44851</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37238,7 +37238,7 @@
         <v>44622</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37311,7 +37311,7 @@
         <v>44622</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37384,7 +37384,7 @@
         <v>45376</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37457,7 +37457,7 @@
         <v>45362</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>45519</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37603,7 +37603,7 @@
         <v>45842</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37676,7 +37676,7 @@
         <v>45467</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37749,7 +37749,7 @@
         <v>45574</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37822,7 +37822,7 @@
         <v>45575</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>46255</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37968,7 +37968,7 @@
         <v>45258</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>45096</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38114,7 +38114,7 @@
         <v>45035</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>44586</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38260,7 +38260,7 @@
         <v>45761</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38333,7 +38333,7 @@
         <v>45089</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45751</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45751</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38562,7 +38562,7 @@
         <v>45624</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45701</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>45394</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38781,7 +38781,7 @@
         <v>45594</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38854,7 +38854,7 @@
         <v>45070</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38927,7 +38927,7 @@
         <v>45310</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39005,7 +39005,7 @@
         <v>45301</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39078,7 +39078,7 @@
         <v>45595</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45394</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39224,7 +39224,7 @@
         <v>45544</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39302,7 +39302,7 @@
         <v>45044</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39375,7 +39375,7 @@
         <v>45474</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45747</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39521,7 +39521,7 @@
         <v>45747</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39594,7 +39594,7 @@
         <v>45747</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39667,7 +39667,7 @@
         <v>44831</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39740,7 +39740,7 @@
         <v>44831</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39813,7 +39813,7 @@
         <v>45317</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39886,7 +39886,7 @@
         <v>45075</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39959,7 +39959,7 @@
         <v>44882</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>45075</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40105,7 +40105,7 @@
         <v>45625</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40178,7 +40178,7 @@
         <v>45070</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>44547</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45259</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40397,7 +40397,7 @@
         <v>45609</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44587</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45313</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45306</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>45096</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40767,7 +40767,7 @@
         <v>45096</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40845,7 +40845,7 @@
         <v>45131</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45328</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40996,7 +40996,7 @@
         <v>45113</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>45301</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>45672</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41215,7 +41215,7 @@
         <v>45266</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41288,7 +41288,7 @@
         <v>44665</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41361,7 +41361,7 @@
         <v>45096</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45641</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45075</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>45394</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>45389</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>44735</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41804,7 +41804,7 @@
         <v>45454</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41877,7 +41877,7 @@
         <v>45422</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>44767</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>45104</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42096,7 +42096,7 @@
         <v>45104</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42169,7 +42169,7 @@
         <v>45385</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>45422</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42315,7 +42315,7 @@
         <v>45422</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42388,7 +42388,7 @@
         <v>44865</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42461,7 +42461,7 @@
         <v>44735</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42534,7 +42534,7 @@
         <v>44735</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42607,7 +42607,7 @@
         <v>45769</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42680,7 +42680,7 @@
         <v>45820</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>45667</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>45677</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45638</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42972,7 +42972,7 @@
         <v>45685</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45881</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43118,7 +43118,7 @@
         <v>45740</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>44866</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43264,7 +43264,7 @@
         <v>46049</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43337,7 +43337,7 @@
         <v>46092</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43410,7 +43410,7 @@
         <v>46092</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>46114</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45775</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>46274</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>

--- a/Översikt TRANEMO.xlsx
+++ b/Översikt TRANEMO.xlsx
@@ -601,7 +601,7 @@
         <v>45523</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45132</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45450</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45087</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45917</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>44739</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>44658</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44770</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44767</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45377</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45397</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>44770</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45484</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>44732</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45621</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>46072</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>44848</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45093</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>45392</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44866</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>44947</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>45906</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45096</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45922</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>45800</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44644</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44609</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>45831</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45328</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>46244</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44706</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>45422</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45638</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45147</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>44800</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>44613</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44574</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>44564</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>44585</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>44637</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>44487</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>44852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44851</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44734</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44599</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44670</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44494</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44804</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44583</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44616</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44887</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44502</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44585</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44872</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44481</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44675</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44882</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44722</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44530</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44680</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44630</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44775</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44837</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44793</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44788</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44800</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>44866</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44522</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44500</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44599</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>44732</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>44735</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44705</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>44599</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>44866</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>44522</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>44552</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45224</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>45701</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45575</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>44882</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45484</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45359</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>44958</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45425</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44867</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44882</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45377</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45747</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45641</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45096</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44838</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45424</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45751</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45044</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45329</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>45211</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45222</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>45099</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>45170</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>45259</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>44586</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44882</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>45763</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45763</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44882</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44887</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>44851</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>45664</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>44855</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>45196</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45317</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>45463</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>45463</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>45391</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45665</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>45342</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44970</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>44866</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45526</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44749</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45362</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45317</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>45415</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>44866</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45574</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45140</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44784</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44958</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45153</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>44552</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>45474</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45183</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>45574</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45467</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45257</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>45539</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45321</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44947</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45245</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45392</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45472</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45883</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>44852</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>45062</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>45819</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>44583</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>45155</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>45467</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>45002</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>45484</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>45270</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45334</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>45096</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45169</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>44867</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>45424</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>45544</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45894</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45897</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45897</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45897</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>45751</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45751</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45259</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45313</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45227</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45743</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45426</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45089</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45574</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>44523</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45306</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>44511</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45303</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45394</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45315</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45327</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45315</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45906</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>44547</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44593</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45362</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45075</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45912</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45810</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>44988</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45362</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>44652</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>45544</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>44665</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>45096</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45328</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45316</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45075</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>45917</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>45187</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>44544</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>45392</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>45392</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45334</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45917</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45641</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45551</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>44958</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45922</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45359</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45616</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45394</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>44656</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45644</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45734</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45377</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45673</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>45701</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>45797</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45439</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44622</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44622</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45595</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45594</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45933</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45679</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45679</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>45316</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45936</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45316</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45544</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45933</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44649</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45399</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45937</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45937</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45572</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45736</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45070</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45377</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45747</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45747</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45937</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45716</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45097</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45937</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45938</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45196</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45939</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45939</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45939</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45624</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45939</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>45939</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45673</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45547</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45897</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45656</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>44665</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45629</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45629</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45266</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>44819</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>44679</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>45816</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>45096</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45096</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45096</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45816</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45814</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45815</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45950</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45713</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45301</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45819</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44965</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45820</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45820</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>45950</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>45701</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45950</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45694</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44699</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>45950</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>45950</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44720</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>45572</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>44596</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45625</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45740</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45747</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45740</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45722</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45737</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45831</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45832</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45131</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45113</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45258</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45157</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45966</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>44799</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45328</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45328</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>45169</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>45174</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>44802</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45701</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>45672</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>45519</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44748</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45761</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45096</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45096</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44725</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45315</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45005</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45832</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45624</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>45848</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45824</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45813</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45716</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45315</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45740</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45210</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45978</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45267</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45978</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45227</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45140</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45978</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45301</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45978</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45978</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45722</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45740</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45978</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45715</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45258</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45035</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45980</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>45715</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>45679</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44831</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>44831</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45876</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>44952</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45747</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45747</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45747</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45877</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45877</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45259</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>45245</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45093</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45740</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45070</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>46099</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45450</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>44537</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45789</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45376</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44904</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>44732</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45251</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45547</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>45774</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>45566</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>44851</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44511</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>46111</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44867</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45551</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45316</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45035</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>45035</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>45993</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45994</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>45363</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45376</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45994</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45993</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>46126</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44867</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>45568</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44578</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>44587</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>44593</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45566</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45813</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45762</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>45188</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>45546</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>45301</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44600</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44656</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>44983</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>44866</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>46010</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45222</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45363</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45079</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45436</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>46013</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45785</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45711</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45688</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45720</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45050</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>45425</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>46013</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>46013</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>46013</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45714</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45714</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>45715</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45695</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>45705</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>44578</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45720</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44902</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>44931</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45670</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>45891</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45227</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45722</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>45467</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>45895</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45825</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45922</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>45044</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44684</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45714</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45587</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>44658</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45174</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35492,7 +35492,7 @@
         <v>45050</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35565,7 +35565,7 @@
         <v>44958</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>45075</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>44977</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44958</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>45034</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44963</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>45762</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45310</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>44998</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45609</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>46051</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>46051</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>46063</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>46072</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>45390</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>46086</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>46086</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>46086</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>46086</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>46160</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46160</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>46160</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>46092</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37254,7 +37254,7 @@
         <v>45772</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>46174</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>46176</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>46178</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>46178</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>46178</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>46182</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>46185</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>46190</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>46185</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>46193</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>46197</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>46203</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>46203</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45888</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>46213</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>46213</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>46213</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>46213</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>46265</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>46265</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>46265</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>46265</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>46265</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>46265</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46265</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46265</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46224</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45922</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>46231</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39454,7 +39454,7 @@
         <v>46277</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>46280</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>46090</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>46282</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>46240</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>46240</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>45789</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>46105</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>46289</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>46289</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>46289</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>45978</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>46289</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>45978</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45978</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>46294</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>46294</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45362</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>45842</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40876,7 +40876,7 @@
         <v>46255</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>46301</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>46303</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>46303</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>46289</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>46303</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>46303</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>46289</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>46289</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>46303</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45394</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>44735</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>44735</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>44735</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45389</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45454</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45422</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>44767</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45104</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45104</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>45385</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45422</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45422</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44865</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>45769</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>45820</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45667</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
         <v>45677</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45638</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45685</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>45881</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45740</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         <v>44866</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43300,7 +43300,7 @@
         <v>46049</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>46092</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>46092</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>46114</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45775</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>46274</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>

--- a/Översikt TRANEMO.xlsx
+++ b/Översikt TRANEMO.xlsx
@@ -601,7 +601,7 @@
         <v>45523</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45132</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45450</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45087</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45917</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>44739</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>44658</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44770</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44767</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45377</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45397</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>44770</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>45484</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>44732</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>45621</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>46072</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>44848</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45093</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>45392</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>45608</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>44866</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>44947</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3742,7 +3742,7 @@
         <v>45906</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>45096</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45922</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4067,7 +4067,7 @@
         <v>45800</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4181,7 +4181,7 @@
         <v>44644</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         <v>45575</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         <v>44609</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4510,7 +4510,7 @@
         <v>45740</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>45831</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>46126</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45328</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>46244</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>44706</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5152,7 +5152,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         <v>45422</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45638</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45147</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>44800</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>44613</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44574</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>44564</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>44585</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>44637</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>44487</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>44852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44851</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44734</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44599</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44670</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44494</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44804</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44583</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44616</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44887</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44502</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44495</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7061,7 +7061,7 @@
         <v>44585</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44872</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44509</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>44537</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>44589</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44481</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44675</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44882</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44722</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44530</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44799</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44680</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44630</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44775</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44837</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>44793</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44788</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8312,7 +8312,7 @@
         <v>44800</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>44866</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44522</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44500</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44599</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>44732</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
         <v>44735</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         <v>44705</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8906,7 +8906,7 @@
         <v>44599</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>44866</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>44522</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9130,7 +9130,7 @@
         <v>44552</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45224</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9281,7 +9281,7 @@
         <v>45701</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9354,7 +9354,7 @@
         <v>45575</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9427,7 +9427,7 @@
         <v>44882</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>45484</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9573,7 +9573,7 @@
         <v>45359</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9646,7 +9646,7 @@
         <v>44958</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9719,7 +9719,7 @@
         <v>45425</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9792,7 +9792,7 @@
         <v>44867</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9865,7 +9865,7 @@
         <v>44882</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45377</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45747</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45747</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45641</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>45096</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>44838</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45424</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>45751</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45044</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45329</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10673,7 +10673,7 @@
         <v>45211</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10746,7 +10746,7 @@
         <v>45222</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>45099</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>45170</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>45259</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>44586</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44882</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>45763</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11257,7 +11257,7 @@
         <v>45763</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44882</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>44887</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>44851</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11549,7 +11549,7 @@
         <v>45664</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11622,7 +11622,7 @@
         <v>44855</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>45196</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45317</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>45463</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>45463</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>45391</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>45665</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>45342</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>44970</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>44866</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45526</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44749</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45362</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45317</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>45415</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>44866</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45574</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45140</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44784</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44958</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45153</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>44552</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>45474</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45183</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>45574</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>45467</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>45257</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13608,7 +13608,7 @@
         <v>45539</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13681,7 +13681,7 @@
         <v>45321</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44947</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13827,7 +13827,7 @@
         <v>45245</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13900,7 +13900,7 @@
         <v>45392</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>45472</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14046,7 +14046,7 @@
         <v>45883</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14119,7 +14119,7 @@
         <v>44852</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>45062</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14265,7 +14265,7 @@
         <v>45819</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14338,7 +14338,7 @@
         <v>44583</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>45155</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14484,7 +14484,7 @@
         <v>45467</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>45002</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14630,7 +14630,7 @@
         <v>45484</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14703,7 +14703,7 @@
         <v>45270</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>45334</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14849,7 +14849,7 @@
         <v>45096</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>45169</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14995,7 +14995,7 @@
         <v>44867</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15068,7 +15068,7 @@
         <v>45424</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15141,7 +15141,7 @@
         <v>45544</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         <v>45894</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15292,7 +15292,7 @@
         <v>45897</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>45897</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15448,7 +15448,7 @@
         <v>45897</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15526,7 +15526,7 @@
         <v>45751</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15604,7 +15604,7 @@
         <v>45751</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15682,7 +15682,7 @@
         <v>45259</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15755,7 +15755,7 @@
         <v>45313</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15828,7 +15828,7 @@
         <v>45227</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15901,7 +15901,7 @@
         <v>45743</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>45426</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16047,7 +16047,7 @@
         <v>45089</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16120,7 +16120,7 @@
         <v>45574</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16193,7 +16193,7 @@
         <v>44523</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16266,7 +16266,7 @@
         <v>45306</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16339,7 +16339,7 @@
         <v>44511</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16412,7 +16412,7 @@
         <v>45303</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16485,7 +16485,7 @@
         <v>45394</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45315</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>45327</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>45315</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45906</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>44547</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16928,7 +16928,7 @@
         <v>44593</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17001,7 +17001,7 @@
         <v>45362</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17074,7 +17074,7 @@
         <v>45075</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45912</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17220,7 +17220,7 @@
         <v>45810</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17298,7 +17298,7 @@
         <v>44988</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>45362</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17444,7 +17444,7 @@
         <v>44652</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17517,7 +17517,7 @@
         <v>45544</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17590,7 +17590,7 @@
         <v>44665</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>45096</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17741,7 +17741,7 @@
         <v>45328</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>45316</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
         <v>45075</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>45917</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18038,7 +18038,7 @@
         <v>45187</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>44544</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>45392</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18257,7 +18257,7 @@
         <v>45392</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18330,7 +18330,7 @@
         <v>45334</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>45917</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45641</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18549,7 +18549,7 @@
         <v>45551</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18622,7 +18622,7 @@
         <v>44958</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18695,7 +18695,7 @@
         <v>45922</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18768,7 +18768,7 @@
         <v>45359</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45616</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45394</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>44656</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>45644</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19133,7 +19133,7 @@
         <v>45734</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19206,7 +19206,7 @@
         <v>45377</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>45673</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19352,7 +19352,7 @@
         <v>45701</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19425,7 +19425,7 @@
         <v>45797</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19498,7 +19498,7 @@
         <v>45439</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19571,7 +19571,7 @@
         <v>44622</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19644,7 +19644,7 @@
         <v>44622</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>45595</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19790,7 +19790,7 @@
         <v>45594</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19863,7 +19863,7 @@
         <v>45933</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19936,7 +19936,7 @@
         <v>45679</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20009,7 +20009,7 @@
         <v>45679</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20082,7 +20082,7 @@
         <v>45316</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20155,7 +20155,7 @@
         <v>45936</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20228,7 +20228,7 @@
         <v>45316</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20301,7 +20301,7 @@
         <v>45544</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20374,7 +20374,7 @@
         <v>45933</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20447,7 +20447,7 @@
         <v>44649</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20520,7 +20520,7 @@
         <v>45399</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20593,7 +20593,7 @@
         <v>45937</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>45937</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45572</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>45736</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>45070</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>45377</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45747</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21104,7 +21104,7 @@
         <v>45747</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21177,7 +21177,7 @@
         <v>45937</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45716</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45097</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45937</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>45938</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45196</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45939</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>45939</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45939</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45624</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21912,7 +21912,7 @@
         <v>45939</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21985,7 +21985,7 @@
         <v>45939</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22058,7 +22058,7 @@
         <v>45673</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22131,7 +22131,7 @@
         <v>45547</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22209,7 +22209,7 @@
         <v>45897</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22287,7 +22287,7 @@
         <v>45656</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22360,7 +22360,7 @@
         <v>44665</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22433,7 +22433,7 @@
         <v>45629</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>45629</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45266</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>44819</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>44679</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>45816</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22871,7 +22871,7 @@
         <v>45096</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45096</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23027,7 +23027,7 @@
         <v>45096</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23100,7 +23100,7 @@
         <v>45816</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23173,7 +23173,7 @@
         <v>45814</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>45815</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23319,7 +23319,7 @@
         <v>45950</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45713</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45301</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23538,7 +23538,7 @@
         <v>45819</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>44965</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23684,7 +23684,7 @@
         <v>45820</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23757,7 +23757,7 @@
         <v>45820</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23830,7 +23830,7 @@
         <v>45950</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23903,7 +23903,7 @@
         <v>45701</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45950</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45694</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24127,7 +24127,7 @@
         <v>44699</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>45950</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>45950</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24346,7 +24346,7 @@
         <v>44720</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>45572</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>44596</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24570,7 +24570,7 @@
         <v>45625</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24643,7 +24643,7 @@
         <v>45740</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24716,7 +24716,7 @@
         <v>45747</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24789,7 +24789,7 @@
         <v>45740</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>45722</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45737</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45831</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>45832</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>45131</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45113</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45258</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45157</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25446,7 +25446,7 @@
         <v>45966</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25519,7 +25519,7 @@
         <v>44799</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45328</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>45328</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>45169</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>45174</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25894,7 +25894,7 @@
         <v>44802</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25967,7 +25967,7 @@
         <v>45701</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26040,7 +26040,7 @@
         <v>45672</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26113,7 +26113,7 @@
         <v>45519</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26186,7 +26186,7 @@
         <v>44748</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45761</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45096</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26410,7 +26410,7 @@
         <v>45096</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26483,7 +26483,7 @@
         <v>44725</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26556,7 +26556,7 @@
         <v>45315</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26629,7 +26629,7 @@
         <v>45005</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45832</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26775,7 +26775,7 @@
         <v>45624</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26848,7 +26848,7 @@
         <v>45848</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26921,7 +26921,7 @@
         <v>45824</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26994,7 +26994,7 @@
         <v>45813</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45716</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45315</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27213,7 +27213,7 @@
         <v>45740</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27286,7 +27286,7 @@
         <v>45210</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27359,7 +27359,7 @@
         <v>45978</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27432,7 +27432,7 @@
         <v>45267</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27505,7 +27505,7 @@
         <v>45978</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27578,7 +27578,7 @@
         <v>45227</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45140</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27724,7 +27724,7 @@
         <v>45978</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>45301</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>45978</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45978</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45722</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45740</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>45978</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45715</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45258</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>45035</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>45980</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>45715</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>45679</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>44831</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>44831</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>45876</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>44952</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>45747</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45747</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45747</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45877</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45877</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45259</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>45245</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45093</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>45740</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45070</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>46099</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45450</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29846,7 +29846,7 @@
         <v>44537</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45789</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29992,7 +29992,7 @@
         <v>45376</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30065,7 +30065,7 @@
         <v>44904</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30138,7 +30138,7 @@
         <v>44732</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45251</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>45547</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30362,7 +30362,7 @@
         <v>45774</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30440,7 +30440,7 @@
         <v>45566</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30513,7 +30513,7 @@
         <v>44851</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>44511</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30659,7 +30659,7 @@
         <v>46111</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30732,7 +30732,7 @@
         <v>44867</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30805,7 +30805,7 @@
         <v>45551</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30878,7 +30878,7 @@
         <v>45316</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30951,7 +30951,7 @@
         <v>45035</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31024,7 +31024,7 @@
         <v>45035</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31097,7 +31097,7 @@
         <v>45993</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31170,7 +31170,7 @@
         <v>45994</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31243,7 +31243,7 @@
         <v>45363</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31321,7 +31321,7 @@
         <v>45376</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45994</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31472,7 +31472,7 @@
         <v>45993</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31545,7 +31545,7 @@
         <v>46126</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31618,7 +31618,7 @@
         <v>44867</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31691,7 +31691,7 @@
         <v>45568</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31764,7 +31764,7 @@
         <v>44578</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31837,7 +31837,7 @@
         <v>44587</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31910,7 +31910,7 @@
         <v>44593</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31983,7 +31983,7 @@
         <v>45566</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45813</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32129,7 +32129,7 @@
         <v>45762</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32202,7 +32202,7 @@
         <v>45188</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>45546</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>45301</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44600</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>44656</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>44983</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32640,7 +32640,7 @@
         <v>44866</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>46010</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45222</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45363</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32937,7 +32937,7 @@
         <v>45079</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33010,7 +33010,7 @@
         <v>45436</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33083,7 +33083,7 @@
         <v>46013</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45785</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45711</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45688</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33375,7 +33375,7 @@
         <v>45720</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45050</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33521,7 +33521,7 @@
         <v>45425</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33594,7 +33594,7 @@
         <v>46013</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33667,7 +33667,7 @@
         <v>46013</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33740,7 +33740,7 @@
         <v>46013</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>45714</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>45714</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>45715</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45695</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>45705</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>44578</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>45720</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>44902</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>44931</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45670</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>45891</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45227</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45722</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>45467</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>45895</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>45825</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>45922</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>45044</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>44684</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35200,7 +35200,7 @@
         <v>45714</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45587</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>44658</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45174</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35492,7 +35492,7 @@
         <v>45050</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35565,7 +35565,7 @@
         <v>44958</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35638,7 +35638,7 @@
         <v>45075</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>44977</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35784,7 +35784,7 @@
         <v>44958</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35857,7 +35857,7 @@
         <v>45034</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35930,7 +35930,7 @@
         <v>44963</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>45762</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45310</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36154,7 +36154,7 @@
         <v>44998</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36227,7 +36227,7 @@
         <v>45609</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36300,7 +36300,7 @@
         <v>46051</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36373,7 +36373,7 @@
         <v>46051</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>46063</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>46072</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36592,7 +36592,7 @@
         <v>45390</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>46086</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36743,7 +36743,7 @@
         <v>46086</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36816,7 +36816,7 @@
         <v>46086</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36889,7 +36889,7 @@
         <v>46086</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36962,7 +36962,7 @@
         <v>46160</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37035,7 +37035,7 @@
         <v>46160</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37108,7 +37108,7 @@
         <v>46160</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37181,7 +37181,7 @@
         <v>46092</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37254,7 +37254,7 @@
         <v>45772</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>46174</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37400,7 +37400,7 @@
         <v>46176</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>46178</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37546,7 +37546,7 @@
         <v>46178</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37619,7 +37619,7 @@
         <v>46178</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>46182</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37765,7 +37765,7 @@
         <v>46185</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>46190</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37911,7 +37911,7 @@
         <v>46185</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>46193</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>46197</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>46203</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>46203</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38276,7 +38276,7 @@
         <v>45888</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38349,7 +38349,7 @@
         <v>46213</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>46213</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>46213</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>46213</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>46265</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38714,7 +38714,7 @@
         <v>46265</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>46265</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>46265</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>46265</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39006,7 +39006,7 @@
         <v>46265</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39079,7 +39079,7 @@
         <v>46265</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39152,7 +39152,7 @@
         <v>46265</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39225,7 +39225,7 @@
         <v>46224</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39303,7 +39303,7 @@
         <v>45922</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39376,7 +39376,7 @@
         <v>46231</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39454,7 +39454,7 @@
         <v>46277</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39527,7 +39527,7 @@
         <v>46280</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39600,7 +39600,7 @@
         <v>46090</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39673,7 +39673,7 @@
         <v>46282</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>46240</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39824,7 +39824,7 @@
         <v>46240</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39902,7 +39902,7 @@
         <v>45789</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -39975,7 +39975,7 @@
         <v>46105</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40053,7 +40053,7 @@
         <v>46289</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>46289</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40209,7 +40209,7 @@
         <v>46289</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40287,7 +40287,7 @@
         <v>45978</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>46289</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>45978</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45978</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>46294</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40657,7 +40657,7 @@
         <v>46294</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45362</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40803,7 +40803,7 @@
         <v>45842</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40876,7 +40876,7 @@
         <v>46255</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40949,7 +40949,7 @@
         <v>46301</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41022,7 +41022,7 @@
         <v>46303</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>46303</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41168,7 +41168,7 @@
         <v>46289</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41246,7 +41246,7 @@
         <v>46303</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41319,7 +41319,7 @@
         <v>46303</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41392,7 +41392,7 @@
         <v>46289</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>46289</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>46303</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45394</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>44735</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>44735</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>44735</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>45389</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45454</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45422</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>44767</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45104</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45104</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>45385</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45422</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45422</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44865</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>45769</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>45820</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45667</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
         <v>45677</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45638</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45685</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>45881</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45740</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         <v>44866</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43300,7 +43300,7 @@
         <v>46049</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>46092</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>46092</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>46114</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>45775</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>46274</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>

--- a/Översikt TRANEMO.xlsx
+++ b/Översikt TRANEMO.xlsx
@@ -601,7 +601,7 @@
         <v>45523</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45132</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45450</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45087</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45917</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>44770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44739</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44767</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>44658</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45377</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>45397</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44770</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>44732</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>46072</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45621</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>44609</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>44848</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45575</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45906</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44866</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>44644</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45392</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44947</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>46126</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>45096</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>45328</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45093</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>46244</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45800</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45740</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>45422</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44706</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45638</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45147</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>44800</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>44613</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44574</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>44564</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>44637</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>44487</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>44585</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>44852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44599</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44851</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44734</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44670</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44494</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44804</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44583</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44616</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44887</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44502</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44585</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44495</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44537</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44675</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44722</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44775</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44599</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44509</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44680</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44799</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44630</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44793</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44800</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44732</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44872</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>44837</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44788</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44522</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44500</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>44705</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44599</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44552</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44958</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44593</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44596</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45316</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45196</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45362</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44998</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45315</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>44656</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45641</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45157</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45270</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45747</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45747</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44732</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44882</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45713</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44947</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45377</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45484</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45327</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>44852</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45551</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45740</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45363</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>44902</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>45566</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44867</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>44931</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>45701</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45574</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45224</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45426</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45259</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45257</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45315</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45301</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45572</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>45694</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>44958</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>44866</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>45467</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45093</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>44988</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>45251</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44799</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>45227</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>44537</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44867</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45763</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45155</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>45751</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45222</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45317</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45099</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44983</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45544</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45763</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>45174</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>44583</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45747</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>45747</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>45734</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>45566</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45096</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45079</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>45044</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>45259</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>45316</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>45467</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45891</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>45436</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>45813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>45245</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>45183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>45587</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45762</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>45140</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45785</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45714</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45222</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44855</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>44904</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>44578</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45153</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45245</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45062</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45701</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44819</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45894</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45897</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45897</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45897</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44544</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45819</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44958</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45743</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45825</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45227</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45670</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45720</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45399</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45425</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45906</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45362</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45715</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45912</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45917</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45917</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>45673</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>44748</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45716</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45922</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44749</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45359</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45933</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45933</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45936</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45547</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45937</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45321</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45937</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45937</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45939</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45939</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45939</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45937</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45425</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45939</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45939</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45938</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45096</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45096</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45897</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44867</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45169</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45679</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45740</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45740</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45950</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45950</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45950</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45950</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45950</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45390</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45484</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44977</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>45644</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45211</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45966</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>46160</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>46160</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>46160</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>45315</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45315</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>44963</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45329</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45978</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45978</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44522</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45978</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45978</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45978</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45978</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>44866</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45980</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44838</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>44958</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>44578</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45546</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45359</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45993</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45993</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45342</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45034</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45174</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45772</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45994</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45994</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>44958</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45722</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>44658</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45624</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44970</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>46010</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46013</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>46013</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>46013</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>46013</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45714</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45705</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45720</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45096</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45695</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45711</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45187</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45688</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45715</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>46174</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45714</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45392</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45679</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45679</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45424</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45424</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>44866</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>45303</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45170</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>46176</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>44965</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>44552</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45922</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>46178</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>46178</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>44720</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44882</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>44652</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>46182</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44882</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>46051</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>46051</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45551</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45316</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45701</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44665</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45656</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45188</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45574</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>46063</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44867</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45140</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>46072</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>46185</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45463</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45463</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45665</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44656</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>46086</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>46086</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>46086</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>46086</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44600</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45526</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45316</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>46092</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>46190</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45664</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>46193</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45673</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>46099</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45789</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45002</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>46185</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45774</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>46111</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45539</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45439</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45376</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>46197</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45005</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45363</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44684</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>44593</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45544</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>44725</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>46126</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45888</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45362</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44802</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>46203</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>46203</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45050</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45762</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45572</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45450</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45895</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45377</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44866</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>45722</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45547</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>45169</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>44699</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>46213</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>46213</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>46213</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45334</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>45035</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>45035</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>46213</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45377</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>44952</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>45267</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45050</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44523</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>46224</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>44511</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44511</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45097</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45210</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>44784</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>45196</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>45922</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>45392</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>45392</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>46231</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>45629</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>45629</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>45736</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45334</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44679</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44851</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>46277</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45568</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>45415</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>46280</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>45716</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45472</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>45227</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45391</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>44866</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>45258</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32542,7 +32542,7 @@
         <v>44887</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>46090</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>44649</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32761,7 +32761,7 @@
         <v>46282</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32834,7 +32834,7 @@
         <v>44851</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32907,7 +32907,7 @@
         <v>46240</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>44622</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44622</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>45376</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45519</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>46240</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45467</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>45574</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>45575</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>45258</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>46105</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45096</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>45035</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>44586</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33944,7 +33944,7 @@
         <v>45761</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>45089</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45751</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45751</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45624</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34319,7 +34319,7 @@
         <v>45701</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>46289</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45394</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>46289</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>45594</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>45070</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>46289</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>46289</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45310</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>45301</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45595</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>45978</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>45978</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45978</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45394</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45544</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45044</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45474</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>45747</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>45747</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>45747</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>44831</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44831</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>45317</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45075</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>44882</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45075</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>46294</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45625</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45070</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>44547</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>45259</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>45609</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44587</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36831,7 +36831,7 @@
         <v>46294</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45313</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45306</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45096</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45096</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>45131</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>45328</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45113</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45301</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>45842</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>45672</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45266</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>44665</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>46301</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45362</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>45096</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>45641</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         <v>45075</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>46289</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>46289</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45616</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>46289</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>46303</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>46303</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>46303</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>46303</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>46255</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45797</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38910,7 +38910,7 @@
         <v>45789</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>46303</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>46265</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>46265</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>46265</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39275,7 +39275,7 @@
         <v>46265</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>46265</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>46265</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>46265</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>46265</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>46310</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>46310</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45816</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45814</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45816</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>45815</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>45820</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>45820</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45819</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45722</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>45737</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>45740</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>46310</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>46310</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45747</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45740</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>45831</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>45832</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>45328</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>45328</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>45832</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45824</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45813</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45848</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45715</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45876</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45877</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45877</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45883</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45394</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45389</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>44735</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45454</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45422</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>44767</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45104</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45104</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>45385</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45422</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45422</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44865</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>44735</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>44735</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45769</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
         <v>45820</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45667</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45677</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>45638</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45685</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         <v>45881</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43300,7 +43300,7 @@
         <v>45740</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>44866</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>46049</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>46092</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>46092</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>46114</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45775</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>46274</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>

--- a/Översikt TRANEMO.xlsx
+++ b/Översikt TRANEMO.xlsx
@@ -601,7 +601,7 @@
         <v>45523</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45132</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45450</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45087</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45917</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>44770</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>44739</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44767</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
         <v>44658</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45377</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45484</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
         <v>45397</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2436,7 +2436,7 @@
         <v>44770</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>44732</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>46072</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>45621</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>45386</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         <v>44726</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>44609</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
         <v>45608</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>44848</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>45575</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>45906</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>45922</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>44866</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3857,7 +3857,7 @@
         <v>44644</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45392</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         <v>44947</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4176,7 +4176,7 @@
         <v>46126</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>45096</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>45328</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45093</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4610,7 +4610,7 @@
         <v>46244</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4715,7 +4715,7 @@
         <v>45800</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45740</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4938,7 +4938,7 @@
         <v>45831</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5043,7 +5043,7 @@
         <v>45422</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5153,7 +5153,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5262,7 +5262,7 @@
         <v>44706</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>45638</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45147</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
         <v>44800</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>44613</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5727,7 +5727,7 @@
         <v>44574</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>44564</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>44637</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         <v>44487</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>44585</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6097,7 +6097,7 @@
         <v>44852</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>44599</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6248,7 +6248,7 @@
         <v>44851</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         <v>44734</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>44670</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44494</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         <v>44804</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6618,7 +6618,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
         <v>44583</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6764,7 +6764,7 @@
         <v>44616</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6837,7 +6837,7 @@
         <v>44887</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6910,7 +6910,7 @@
         <v>44502</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>44585</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         <v>44495</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7139,7 +7139,7 @@
         <v>44537</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7290,7 +7290,7 @@
         <v>44675</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>44722</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>44775</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7509,7 +7509,7 @@
         <v>44599</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>44509</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>44680</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>44799</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7801,7 +7801,7 @@
         <v>44630</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         <v>44793</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7947,7 +7947,7 @@
         <v>44800</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8020,7 +8020,7 @@
         <v>44732</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         <v>44872</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>44882</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44530</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
         <v>44837</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>44788</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8463,7 +8463,7 @@
         <v>44522</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>44500</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8682,7 +8682,7 @@
         <v>44705</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8755,7 +8755,7 @@
         <v>44599</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>44552</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44958</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8974,7 +8974,7 @@
         <v>44593</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>44596</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>45316</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>45196</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
         <v>45362</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9344,7 +9344,7 @@
         <v>44998</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9417,7 +9417,7 @@
         <v>45315</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9490,7 +9490,7 @@
         <v>44656</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>45641</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9636,7 +9636,7 @@
         <v>45157</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45270</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         <v>45747</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>45747</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>44732</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44882</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>45713</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>44947</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45377</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45484</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45327</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>44852</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45551</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10585,7 +10585,7 @@
         <v>45740</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10658,7 +10658,7 @@
         <v>45363</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>44902</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10804,7 +10804,7 @@
         <v>45566</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10877,7 +10877,7 @@
         <v>44867</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10950,7 +10950,7 @@
         <v>44931</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>45701</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45574</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45224</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>45426</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45259</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45257</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45315</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45301</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45572</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11690,7 +11690,7 @@
         <v>45694</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>44958</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>44866</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>45467</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11992,7 +11992,7 @@
         <v>45093</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>44988</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12138,7 +12138,7 @@
         <v>45251</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
         <v>44799</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12284,7 +12284,7 @@
         <v>45227</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>44537</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44867</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45763</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>45155</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>45751</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12727,7 +12727,7 @@
         <v>45222</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45317</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12873,7 +12873,7 @@
         <v>45099</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44983</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>45544</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45763</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13165,7 +13165,7 @@
         <v>45174</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13238,7 +13238,7 @@
         <v>44583</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>45747</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13384,7 +13384,7 @@
         <v>45747</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13457,7 +13457,7 @@
         <v>45734</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>45566</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13603,7 +13603,7 @@
         <v>45096</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13676,7 +13676,7 @@
         <v>45079</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>45044</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>45259</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13895,7 +13895,7 @@
         <v>45316</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13968,7 +13968,7 @@
         <v>45467</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45891</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14114,7 +14114,7 @@
         <v>45436</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14187,7 +14187,7 @@
         <v>45813</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14260,7 +14260,7 @@
         <v>45245</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>45183</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14406,7 +14406,7 @@
         <v>45587</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14479,7 +14479,7 @@
         <v>45762</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14552,7 +14552,7 @@
         <v>45140</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14625,7 +14625,7 @@
         <v>45785</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>45714</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14771,7 +14771,7 @@
         <v>45222</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>44855</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14917,7 +14917,7 @@
         <v>44904</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14990,7 +14990,7 @@
         <v>44578</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15063,7 +15063,7 @@
         <v>45153</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         <v>45245</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>45062</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>45701</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15355,7 +15355,7 @@
         <v>44819</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15428,7 +15428,7 @@
         <v>45894</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15501,7 +15501,7 @@
         <v>45897</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15579,7 +15579,7 @@
         <v>45897</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15657,7 +15657,7 @@
         <v>45897</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15735,7 +15735,7 @@
         <v>44544</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15808,7 +15808,7 @@
         <v>45819</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>44958</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15954,7 +15954,7 @@
         <v>45743</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16027,7 +16027,7 @@
         <v>45825</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45227</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>45670</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45720</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16319,7 +16319,7 @@
         <v>45399</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16392,7 +16392,7 @@
         <v>45425</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>45906</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16543,7 +16543,7 @@
         <v>45362</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
         <v>45810</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16694,7 +16694,7 @@
         <v>45715</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16767,7 +16767,7 @@
         <v>45912</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16840,7 +16840,7 @@
         <v>45917</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>45917</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16986,7 +16986,7 @@
         <v>45673</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17059,7 +17059,7 @@
         <v>44748</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17137,7 +17137,7 @@
         <v>45716</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45922</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17283,7 +17283,7 @@
         <v>44749</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17356,7 +17356,7 @@
         <v>45359</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45933</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17502,7 +17502,7 @@
         <v>45933</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17575,7 +17575,7 @@
         <v>45936</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17648,7 +17648,7 @@
         <v>45547</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17726,7 +17726,7 @@
         <v>45937</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45321</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17872,7 +17872,7 @@
         <v>45937</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>45937</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45939</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>45939</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
         <v>45939</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45937</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45425</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>45939</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18456,7 +18456,7 @@
         <v>45939</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18529,7 +18529,7 @@
         <v>45938</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45096</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18675,7 +18675,7 @@
         <v>45096</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45897</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>44867</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
         <v>45169</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18972,7 +18972,7 @@
         <v>45679</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19045,7 +19045,7 @@
         <v>45740</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45740</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45950</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19264,7 +19264,7 @@
         <v>45950</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19337,7 +19337,7 @@
         <v>45950</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19410,7 +19410,7 @@
         <v>45950</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45950</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19556,7 +19556,7 @@
         <v>45390</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19634,7 +19634,7 @@
         <v>45484</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19707,7 +19707,7 @@
         <v>44977</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19780,7 +19780,7 @@
         <v>45644</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>45211</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19926,7 +19926,7 @@
         <v>45966</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19999,7 +19999,7 @@
         <v>46160</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>46160</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>46160</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>45315</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45315</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20364,7 +20364,7 @@
         <v>44963</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20437,7 +20437,7 @@
         <v>45329</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>45978</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20583,7 +20583,7 @@
         <v>45978</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>44522</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>45978</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45978</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45978</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45978</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>44866</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45980</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44838</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21245,7 +21245,7 @@
         <v>44958</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>44578</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21391,7 +21391,7 @@
         <v>45546</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45359</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45993</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21610,7 +21610,7 @@
         <v>45993</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45342</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45034</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21829,7 +21829,7 @@
         <v>45174</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45772</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45994</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22048,7 +22048,7 @@
         <v>45994</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22121,7 +22121,7 @@
         <v>44958</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45722</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>44658</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22340,7 +22340,7 @@
         <v>45624</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22413,7 +22413,7 @@
         <v>44970</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>46010</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22559,7 +22559,7 @@
         <v>46013</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22632,7 +22632,7 @@
         <v>46013</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>46013</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>46013</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22851,7 +22851,7 @@
         <v>45714</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>45705</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45720</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45096</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23143,7 +23143,7 @@
         <v>45695</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45711</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45187</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45688</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>45715</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23508,7 +23508,7 @@
         <v>46174</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23581,7 +23581,7 @@
         <v>45714</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23654,7 +23654,7 @@
         <v>45392</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45679</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45679</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45424</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45424</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>44866</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24097,7 +24097,7 @@
         <v>45303</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45170</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>46176</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>44965</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>44552</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>45922</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>46178</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>46178</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>44720</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24754,7 +24754,7 @@
         <v>44882</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>44652</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>46182</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24973,7 +24973,7 @@
         <v>44882</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25046,7 +25046,7 @@
         <v>46051</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25119,7 +25119,7 @@
         <v>46051</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25192,7 +25192,7 @@
         <v>45551</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25265,7 +25265,7 @@
         <v>45316</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25338,7 +25338,7 @@
         <v>45701</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>44665</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45656</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25557,7 +25557,7 @@
         <v>45188</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25630,7 +25630,7 @@
         <v>45574</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>46063</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>44867</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45140</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>46072</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>46185</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>45463</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>45463</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26214,7 +26214,7 @@
         <v>45665</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44656</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>46086</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>46086</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>46086</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26579,7 +26579,7 @@
         <v>46086</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>44600</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26725,7 +26725,7 @@
         <v>45526</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45316</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26871,7 +26871,7 @@
         <v>46092</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>46190</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27017,7 +27017,7 @@
         <v>45664</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27090,7 +27090,7 @@
         <v>46193</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>45673</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>46099</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27309,7 +27309,7 @@
         <v>45789</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         <v>45002</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27455,7 +27455,7 @@
         <v>46185</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27528,7 +27528,7 @@
         <v>45774</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>46111</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27679,7 +27679,7 @@
         <v>45539</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         <v>45439</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27825,7 +27825,7 @@
         <v>45376</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>46197</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45005</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28049,7 +28049,7 @@
         <v>45363</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28127,7 +28127,7 @@
         <v>44684</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28200,7 +28200,7 @@
         <v>44593</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28273,7 +28273,7 @@
         <v>45544</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>44725</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>46126</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28492,7 +28492,7 @@
         <v>45888</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28565,7 +28565,7 @@
         <v>45362</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28638,7 +28638,7 @@
         <v>44802</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>46203</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>46203</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28857,7 +28857,7 @@
         <v>45050</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -28930,7 +28930,7 @@
         <v>45762</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29003,7 +29003,7 @@
         <v>45572</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45450</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45895</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45377</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29300,7 +29300,7 @@
         <v>44866</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29378,7 +29378,7 @@
         <v>45722</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45547</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>45169</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>44699</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29675,7 +29675,7 @@
         <v>46213</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29748,7 +29748,7 @@
         <v>46213</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>46213</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29894,7 +29894,7 @@
         <v>45334</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -29967,7 +29967,7 @@
         <v>45035</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30040,7 +30040,7 @@
         <v>45035</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>46213</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45377</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30259,7 +30259,7 @@
         <v>44952</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>45267</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30405,7 +30405,7 @@
         <v>45050</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30478,7 +30478,7 @@
         <v>44523</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30551,7 +30551,7 @@
         <v>46224</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30629,7 +30629,7 @@
         <v>44511</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30702,7 +30702,7 @@
         <v>44511</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30775,7 +30775,7 @@
         <v>45097</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30848,7 +30848,7 @@
         <v>45210</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -30921,7 +30921,7 @@
         <v>44784</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -30994,7 +30994,7 @@
         <v>45196</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>45922</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31140,7 +31140,7 @@
         <v>45392</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>45392</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31286,7 +31286,7 @@
         <v>46231</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>45629</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>45629</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>45736</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>45334</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>44679</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>44851</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>46277</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45568</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -31948,7 +31948,7 @@
         <v>45415</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>46280</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32094,7 +32094,7 @@
         <v>45716</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32172,7 +32172,7 @@
         <v>45472</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32245,7 +32245,7 @@
         <v>45227</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32318,7 +32318,7 @@
         <v>45391</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32391,7 +32391,7 @@
         <v>44866</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32469,7 +32469,7 @@
         <v>45258</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32542,7 +32542,7 @@
         <v>44887</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32615,7 +32615,7 @@
         <v>46090</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32688,7 +32688,7 @@
         <v>44649</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32761,7 +32761,7 @@
         <v>46282</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32834,7 +32834,7 @@
         <v>44851</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -32907,7 +32907,7 @@
         <v>46240</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -32985,7 +32985,7 @@
         <v>44622</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33058,7 +33058,7 @@
         <v>44622</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>45376</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33204,7 +33204,7 @@
         <v>45519</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>46240</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33355,7 +33355,7 @@
         <v>45467</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>45574</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>45575</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>45258</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33647,7 +33647,7 @@
         <v>46105</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33725,7 +33725,7 @@
         <v>45096</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33798,7 +33798,7 @@
         <v>45035</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33871,7 +33871,7 @@
         <v>44586</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -33944,7 +33944,7 @@
         <v>45761</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>45089</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34090,7 +34090,7 @@
         <v>45751</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45751</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34246,7 +34246,7 @@
         <v>45624</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34319,7 +34319,7 @@
         <v>45701</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>46289</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45394</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>46289</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34621,7 +34621,7 @@
         <v>45594</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34694,7 +34694,7 @@
         <v>45070</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>46289</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>46289</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45310</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35001,7 +35001,7 @@
         <v>45301</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35074,7 +35074,7 @@
         <v>45595</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35147,7 +35147,7 @@
         <v>45978</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35220,7 +35220,7 @@
         <v>45978</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35293,7 +35293,7 @@
         <v>45978</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45394</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35439,7 +35439,7 @@
         <v>45544</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35517,7 +35517,7 @@
         <v>45044</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35590,7 +35590,7 @@
         <v>45474</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35663,7 +35663,7 @@
         <v>45747</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35736,7 +35736,7 @@
         <v>45747</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35809,7 +35809,7 @@
         <v>45747</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35882,7 +35882,7 @@
         <v>44831</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35955,7 +35955,7 @@
         <v>44831</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36028,7 +36028,7 @@
         <v>45317</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>45075</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36174,7 +36174,7 @@
         <v>44882</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>45075</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>46294</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45625</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45070</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>44547</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>45259</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>45609</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>44587</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36831,7 +36831,7 @@
         <v>46294</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45313</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>45306</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>45096</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45096</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37206,7 +37206,7 @@
         <v>45131</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>45328</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45113</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45301</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>45842</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>45672</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45266</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>44665</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>46301</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>45362</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37941,7 +37941,7 @@
         <v>45096</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>45641</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         <v>45075</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>46289</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>46289</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38321,7 +38321,7 @@
         <v>45616</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38394,7 +38394,7 @@
         <v>46289</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38472,7 +38472,7 @@
         <v>46303</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38545,7 +38545,7 @@
         <v>46303</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>46303</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38691,7 +38691,7 @@
         <v>46303</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>46255</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38837,7 +38837,7 @@
         <v>45797</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38910,7 +38910,7 @@
         <v>45789</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>46303</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>46265</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>46265</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>46265</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39275,7 +39275,7 @@
         <v>46265</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39348,7 +39348,7 @@
         <v>46265</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39421,7 +39421,7 @@
         <v>46265</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39494,7 +39494,7 @@
         <v>46265</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>46265</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39640,7 +39640,7 @@
         <v>46310</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>46310</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39786,7 +39786,7 @@
         <v>45816</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39859,7 +39859,7 @@
         <v>45814</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39932,7 +39932,7 @@
         <v>45816</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40005,7 +40005,7 @@
         <v>45815</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>45820</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40151,7 +40151,7 @@
         <v>45820</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40224,7 +40224,7 @@
         <v>45819</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45722</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40370,7 +40370,7 @@
         <v>45737</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40443,7 +40443,7 @@
         <v>45740</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40516,7 +40516,7 @@
         <v>46310</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>46310</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40662,7 +40662,7 @@
         <v>45747</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40735,7 +40735,7 @@
         <v>45740</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40808,7 +40808,7 @@
         <v>45831</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40881,7 +40881,7 @@
         <v>45832</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -40954,7 +40954,7 @@
         <v>45328</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>45328</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41110,7 +41110,7 @@
         <v>45832</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45824</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41256,7 +41256,7 @@
         <v>45813</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41329,7 +41329,7 @@
         <v>45848</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41402,7 +41402,7 @@
         <v>45715</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
         <v>45876</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45877</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41621,7 +41621,7 @@
         <v>45877</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41694,7 +41694,7 @@
         <v>45883</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41767,7 +41767,7 @@
         <v>45394</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41840,7 +41840,7 @@
         <v>45389</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41913,7 +41913,7 @@
         <v>44735</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -41986,7 +41986,7 @@
         <v>45454</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42059,7 +42059,7 @@
         <v>45422</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42132,7 +42132,7 @@
         <v>44767</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42205,7 +42205,7 @@
         <v>45104</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42278,7 +42278,7 @@
         <v>45104</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42351,7 +42351,7 @@
         <v>45385</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42424,7 +42424,7 @@
         <v>45422</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         <v>45422</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44865</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42643,7 +42643,7 @@
         <v>44735</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42716,7 +42716,7 @@
         <v>44735</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>45769</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42862,7 +42862,7 @@
         <v>45820</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42935,7 +42935,7 @@
         <v>45667</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>45677</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43081,7 +43081,7 @@
         <v>45638</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43154,7 +43154,7 @@
         <v>45685</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43227,7 +43227,7 @@
         <v>45881</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43300,7 +43300,7 @@
         <v>45740</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43373,7 +43373,7 @@
         <v>44866</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>46049</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>46092</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>46092</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>46114</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45775</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43811,7 +43811,7 @@
         <v>46274</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>

--- a/Översikt TRANEMO.xlsx
+++ b/Översikt TRANEMO.xlsx
@@ -601,7 +601,7 @@
         <v>45523</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45132</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45450</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45087</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45917</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>44739</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>44658</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44770</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44767</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45377</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45621</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45397</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44770</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>46072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>45484</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>46317</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>44732</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>44726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45328</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>45906</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45922</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>44848</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45392</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45608</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44866</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45800</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>45740</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>45831</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>46126</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45575</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>44609</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45093</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>44947</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45096</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44644</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>44706</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>45422</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>45638</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>45147</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44800</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44564</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44585</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>44637</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44851</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44734</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44852</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>44670</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44494</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>44804</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44583</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44616</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>44887</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>44502</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44585</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44495</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44537</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44675</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>44722</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>44775</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44599</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44509</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>44680</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>44799</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44630</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44793</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44800</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44732</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>44872</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>44530</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44882</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>44837</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44788</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44522</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44500</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>44705</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44587</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>44593</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>45566</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>45062</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>44599</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44958</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>45153</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>45819</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>45188</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>45546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>45183</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45301</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45211</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45222</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>44600</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45894</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>44656</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>44983</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>44866</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45897</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>45897</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>45222</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>45363</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>45526</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>45897</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45079</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45362</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45415</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45050</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44866</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45425</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45743</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44578</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>45245</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>45883</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>44866</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>44902</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>44931</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>45906</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>45722</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45912</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>45810</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45224</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>45917</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>45044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44684</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>45917</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45922</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>44658</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45174</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>45050</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44958</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>45075</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>44977</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45772</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44958</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44963</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45933</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45936</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45359</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45933</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45310</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45425</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45937</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45937</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45937</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44867</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44998</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44882</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45937</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45938</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45939</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45939</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45939</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>46174</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>45939</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45609</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45939</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45747</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>45747</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>44838</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45424</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45897</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45701</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45575</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44882</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45484</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>44882</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>44887</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44851</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>46176</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>44958</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>44855</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45463</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>45463</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45391</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44866</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45377</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45641</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>45950</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45950</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45950</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45950</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45950</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45044</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45329</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>46182</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45099</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45170</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45259</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>46185</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45664</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45317</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45665</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45342</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45966</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>44970</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44749</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45317</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>46190</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44866</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>46185</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>46193</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>44784</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>46197</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45474</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>45539</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45978</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45978</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45978</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45978</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45978</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45321</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45978</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45392</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45980</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>46203</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>46203</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45155</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45334</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45888</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45751</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45751</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45259</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>45313</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45227</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>45574</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>46213</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>45467</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>45993</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45257</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>46213</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45994</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46213</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>46213</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45994</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45993</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>44947</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45315</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45327</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45315</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45472</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>46224</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45922</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>46231</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45096</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>44852</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>46277</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45075</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>46010</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>46280</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>46013</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45711</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45688</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>46090</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>45720</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>46013</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>46013</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>45641</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>46013</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>45714</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>45714</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>45715</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45695</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45705</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45616</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>46282</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>46240</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>45922</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>46240</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44583</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>46105</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45797</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>46289</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>46051</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>46051</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>46289</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>46289</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45978</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>46289</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45978</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>46294</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>46063</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45816</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45816</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46294</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>45814</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45815</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>46072</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45467</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45819</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>45820</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>45820</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>45484</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45740</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>45747</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45740</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45722</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45737</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>45831</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45832</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>46086</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>46086</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>46086</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>46086</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>45169</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>46092</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45362</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45328</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45328</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45842</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>44867</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>46099</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45789</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45832</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45848</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45824</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45813</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>46255</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>45774</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>46301</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>46111</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>46303</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45426</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46289</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45363</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>45376</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45089</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44523</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45715</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>46303</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>46303</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>46289</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>46289</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>46126</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>46303</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45876</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>46265</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>46265</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>44511</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45877</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45877</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>46265</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>46265</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>45303</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>46265</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>46265</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>44547</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>44593</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>46265</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>46265</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45362</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45140</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45075</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45813</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45762</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44988</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45362</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44652</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45544</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>44665</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>46310</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46310</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46310</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45436</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>46310</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>46303</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45785</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45720</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>46178</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45551</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>44958</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>45670</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>45891</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>45227</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45359</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>45467</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45895</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>45825</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45714</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45587</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45762</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>46315</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>45789</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>46317</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45439</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>45595</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>45594</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>46317</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>46317</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>46317</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>45679</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45679</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>45544</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45399</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45070</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45377</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45097</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>45624</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>44665</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>45629</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>45629</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45390</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45266</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>46160</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>46160</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>46160</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45301</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>44965</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>44699</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45625</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>45131</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45174</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>44802</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>45701</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45672</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45519</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45096</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45096</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>45005</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>45740</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45140</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>45722</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>45715</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>45035</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45679</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>44831</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>44831</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45093</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45740</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45070</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44537</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45251</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>44851</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>44867</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45551</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45035</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45035</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44522</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44882</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>45096</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45751</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>44586</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45763</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>45763</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>45196</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45574</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44552</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45002</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45270</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45096</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45424</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45544</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45574</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45306</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45394</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45328</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45316</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45187</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>44544</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45392</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45392</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45334</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45394</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>44656</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45644</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>45734</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>45377</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45673</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>45701</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>44622</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44622</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45316</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45316</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44649</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45572</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>45736</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45747</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>45747</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>45716</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45196</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45673</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45547</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45656</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44819</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44679</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>45096</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>45096</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45096</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>45713</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39240,7 +39240,7 @@
         <v>45701</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>45694</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>44720</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45572</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>44596</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45113</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45258</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>45157</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>44799</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>45169</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>44748</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45761</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>44725</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45315</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45624</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45716</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45315</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45210</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45267</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45227</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>45301</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>45740</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45258</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>44952</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45747</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45747</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>45747</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>45259</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45245</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45450</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>45376</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>44904</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>44732</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45547</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>45566</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>44511</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41893,7 +41893,7 @@
         <v>45316</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>44867</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>45568</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>44578</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>45394</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>44735</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44735</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>44735</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45389</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>45454</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45422</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>44767</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>45104</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45104</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45385</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45422</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>45422</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>44865</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>45769</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45820</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>45667</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45677</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>45638</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>45685</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>45881</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>45740</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43791,7 +43791,7 @@
         <v>44866</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>46049</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>46092</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44010,7 +44010,7 @@
         <v>46092</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>46114</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>45775</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>46274</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>

--- a/Översikt TRANEMO.xlsx
+++ b/Översikt TRANEMO.xlsx
@@ -601,7 +601,7 @@
         <v>45523</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45132</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         <v>45450</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>45087</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>45917</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>44739</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>44658</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1552,7 +1552,7 @@
         <v>44770</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>44767</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>45261</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45377</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>44960</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2113,7 +2113,7 @@
         <v>45422</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45621</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
         <v>45397</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2440,7 +2440,7 @@
         <v>44770</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>46072</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2656,7 +2656,7 @@
         <v>45484</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>46317</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>44732</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2984,7 +2984,7 @@
         <v>45386</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3099,7 +3099,7 @@
         <v>44726</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>45328</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>45906</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45922</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>44848</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3638,7 +3638,7 @@
         <v>45392</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45608</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>44866</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>45800</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <v>45740</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>45831</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>46244</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>46126</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>45575</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4614,7 +4614,7 @@
         <v>44609</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45093</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4834,7 +4834,7 @@
         <v>44947</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4939,7 +4939,7 @@
         <v>45096</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44644</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5154,7 +5154,7 @@
         <v>44706</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>44706</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
         <v>45422</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5482,7 +5482,7 @@
         <v>45638</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>45147</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>44800</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5765,7 +5765,7 @@
         <v>44613</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>44574</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         <v>44564</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>44585</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6062,7 +6062,7 @@
         <v>44637</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6135,7 +6135,7 @@
         <v>44599</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>44851</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44734</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6354,7 +6354,7 @@
         <v>44852</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6432,7 +6432,7 @@
         <v>44670</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6510,7 +6510,7 @@
         <v>44494</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>44804</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44583</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6802,7 +6802,7 @@
         <v>44616</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6875,7 +6875,7 @@
         <v>44887</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>44502</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         <v>44585</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>44495</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44537</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7250,7 +7250,7 @@
         <v>44589</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44675</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>44722</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>44775</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>44599</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>44509</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>44680</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>44799</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44630</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44793</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>44800</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>44732</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>44872</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>44530</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44882</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>44837</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44788</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44522</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44500</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>44705</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>44587</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>44593</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>45566</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>45062</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>44599</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44958</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>45153</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>45819</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
         <v>44552</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9450,7 +9450,7 @@
         <v>45188</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>45546</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         <v>45183</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45301</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>45211</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>45222</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9888,7 +9888,7 @@
         <v>44600</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45894</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>44656</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>44983</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>44866</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45897</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>45897</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>45222</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>45363</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>45526</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10633,7 +10633,7 @@
         <v>45897</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45079</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10784,7 +10784,7 @@
         <v>45362</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>45415</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10930,7 +10930,7 @@
         <v>45050</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44866</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>45425</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11154,7 +11154,7 @@
         <v>45743</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>44578</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>45245</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11373,7 +11373,7 @@
         <v>45883</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>44866</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>44902</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11597,7 +11597,7 @@
         <v>44931</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>45906</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11748,7 +11748,7 @@
         <v>45722</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11821,7 +11821,7 @@
         <v>45912</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         <v>45810</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11972,7 +11972,7 @@
         <v>45224</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>45917</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>45044</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>44684</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>45917</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45922</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>44658</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12488,7 +12488,7 @@
         <v>45174</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>45050</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12634,7 +12634,7 @@
         <v>44958</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12707,7 +12707,7 @@
         <v>45075</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>44977</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12853,7 +12853,7 @@
         <v>45772</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44958</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12999,7 +12999,7 @@
         <v>45034</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>44963</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13145,7 +13145,7 @@
         <v>45933</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45936</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45359</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>45933</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>45310</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13515,7 +13515,7 @@
         <v>45425</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45937</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13661,7 +13661,7 @@
         <v>45937</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45937</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13807,7 +13807,7 @@
         <v>44867</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13880,7 +13880,7 @@
         <v>44998</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44882</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14026,7 +14026,7 @@
         <v>45937</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>45938</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14172,7 +14172,7 @@
         <v>45939</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14245,7 +14245,7 @@
         <v>45939</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14318,7 +14318,7 @@
         <v>45939</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>46174</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>45939</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>45609</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45939</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>45747</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>45747</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>44838</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14902,7 +14902,7 @@
         <v>45424</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>45897</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45701</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45575</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>44882</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45484</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>44882</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15418,7 +15418,7 @@
         <v>44887</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15491,7 +15491,7 @@
         <v>44851</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15564,7 +15564,7 @@
         <v>46176</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15637,7 +15637,7 @@
         <v>44958</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15710,7 +15710,7 @@
         <v>44855</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>45463</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>45463</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15929,7 +15929,7 @@
         <v>45391</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16002,7 +16002,7 @@
         <v>44866</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -16080,7 +16080,7 @@
         <v>45377</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45641</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16226,7 +16226,7 @@
         <v>45950</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16299,7 +16299,7 @@
         <v>45950</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16372,7 +16372,7 @@
         <v>45950</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16445,7 +16445,7 @@
         <v>45950</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16518,7 +16518,7 @@
         <v>45950</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16591,7 +16591,7 @@
         <v>46178</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>45044</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45329</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>46182</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16883,7 +16883,7 @@
         <v>45099</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>45170</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -17029,7 +17029,7 @@
         <v>45259</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>46185</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17175,7 +17175,7 @@
         <v>45664</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17248,7 +17248,7 @@
         <v>45317</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17321,7 +17321,7 @@
         <v>45665</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17394,7 +17394,7 @@
         <v>45342</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>45966</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17540,7 +17540,7 @@
         <v>44970</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17613,7 +17613,7 @@
         <v>44749</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17686,7 +17686,7 @@
         <v>45317</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>46190</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44866</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17910,7 +17910,7 @@
         <v>46185</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17983,7 +17983,7 @@
         <v>46193</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>44784</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18129,7 +18129,7 @@
         <v>46197</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18202,7 +18202,7 @@
         <v>45474</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18275,7 +18275,7 @@
         <v>45539</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18348,7 +18348,7 @@
         <v>45978</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18421,7 +18421,7 @@
         <v>45978</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45978</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18567,7 +18567,7 @@
         <v>45978</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18640,7 +18640,7 @@
         <v>45978</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18713,7 +18713,7 @@
         <v>45321</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18786,7 +18786,7 @@
         <v>45978</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18859,7 +18859,7 @@
         <v>45392</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>45980</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>46203</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>46203</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>45155</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
         <v>45334</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19297,7 +19297,7 @@
         <v>45888</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>45751</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19448,7 +19448,7 @@
         <v>45751</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19526,7 +19526,7 @@
         <v>45259</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19599,7 +19599,7 @@
         <v>45313</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19672,7 +19672,7 @@
         <v>45227</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19745,7 +19745,7 @@
         <v>45574</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19823,7 +19823,7 @@
         <v>46213</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19896,7 +19896,7 @@
         <v>45467</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19969,7 +19969,7 @@
         <v>45993</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45257</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>46213</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20188,7 +20188,7 @@
         <v>45994</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20261,7 +20261,7 @@
         <v>46213</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20334,7 +20334,7 @@
         <v>46213</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20407,7 +20407,7 @@
         <v>45994</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20480,7 +20480,7 @@
         <v>45993</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20553,7 +20553,7 @@
         <v>44947</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>45315</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20699,7 +20699,7 @@
         <v>45327</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45315</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>45472</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>46224</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>45922</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21069,7 +21069,7 @@
         <v>46231</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>45096</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>44852</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21298,7 +21298,7 @@
         <v>46277</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21371,7 +21371,7 @@
         <v>45075</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21444,7 +21444,7 @@
         <v>46010</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21517,7 +21517,7 @@
         <v>46280</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>46013</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21663,7 +21663,7 @@
         <v>45711</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45688</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21809,7 +21809,7 @@
         <v>46090</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21882,7 +21882,7 @@
         <v>45720</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21955,7 +21955,7 @@
         <v>46013</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -22028,7 +22028,7 @@
         <v>46013</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22101,7 +22101,7 @@
         <v>45641</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22174,7 +22174,7 @@
         <v>46013</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22247,7 +22247,7 @@
         <v>45714</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>45714</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>45715</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45695</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45705</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>45616</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>46282</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22758,7 +22758,7 @@
         <v>46240</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22836,7 +22836,7 @@
         <v>45922</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22909,7 +22909,7 @@
         <v>46240</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22987,7 +22987,7 @@
         <v>44583</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23060,7 +23060,7 @@
         <v>46105</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23138,7 +23138,7 @@
         <v>45797</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>46289</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>46051</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>46051</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23435,7 +23435,7 @@
         <v>46289</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>46289</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45978</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>46289</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45978</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45978</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>46294</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23961,7 +23961,7 @@
         <v>46063</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -24034,7 +24034,7 @@
         <v>45816</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24107,7 +24107,7 @@
         <v>45816</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24180,7 +24180,7 @@
         <v>46294</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24253,7 +24253,7 @@
         <v>45814</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45815</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24399,7 +24399,7 @@
         <v>46072</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24472,7 +24472,7 @@
         <v>45467</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>45819</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24618,7 +24618,7 @@
         <v>45820</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24691,7 +24691,7 @@
         <v>45820</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24764,7 +24764,7 @@
         <v>45484</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24837,7 +24837,7 @@
         <v>45740</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24910,7 +24910,7 @@
         <v>45747</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>45740</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45722</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25129,7 +25129,7 @@
         <v>45737</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>45831</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25275,7 +25275,7 @@
         <v>45832</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25348,7 +25348,7 @@
         <v>46086</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25421,7 +25421,7 @@
         <v>46086</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>46086</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25567,7 +25567,7 @@
         <v>46086</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>45169</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>46092</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25786,7 +25786,7 @@
         <v>45362</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25859,7 +25859,7 @@
         <v>45328</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25937,7 +25937,7 @@
         <v>45328</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45842</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>44867</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>46099</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45789</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45832</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45848</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45824</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45813</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26599,7 +26599,7 @@
         <v>46255</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26672,7 +26672,7 @@
         <v>45774</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>46301</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>46111</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>46303</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45426</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46289</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45363</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27198,7 +27198,7 @@
         <v>45376</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45089</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44523</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45715</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>46303</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         <v>46303</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>46289</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>46289</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27797,7 +27797,7 @@
         <v>46126</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>46303</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         <v>45876</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>46265</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>46265</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28162,7 +28162,7 @@
         <v>44511</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>45877</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28308,7 +28308,7 @@
         <v>45877</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -28381,7 +28381,7 @@
         <v>46265</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -28454,7 +28454,7 @@
         <v>46265</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         <v>45303</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -28600,7 +28600,7 @@
         <v>46265</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -28673,7 +28673,7 @@
         <v>46265</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -28746,7 +28746,7 @@
         <v>44547</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -28819,7 +28819,7 @@
         <v>44593</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>46265</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>46265</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>45362</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45140</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -29184,7 +29184,7 @@
         <v>45075</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45813</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -29330,7 +29330,7 @@
         <v>45762</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -29403,7 +29403,7 @@
         <v>44988</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45362</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44652</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -29622,7 +29622,7 @@
         <v>45544</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -29695,7 +29695,7 @@
         <v>44665</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>46310</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>46310</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -29914,7 +29914,7 @@
         <v>46310</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -29987,7 +29987,7 @@
         <v>45436</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -30060,7 +30060,7 @@
         <v>46310</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>46303</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -30206,7 +30206,7 @@
         <v>45785</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -30279,7 +30279,7 @@
         <v>45720</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -30352,7 +30352,7 @@
         <v>46178</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45551</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -30498,7 +30498,7 @@
         <v>44958</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>45670</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -30644,7 +30644,7 @@
         <v>45891</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -30717,7 +30717,7 @@
         <v>45227</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -30790,7 +30790,7 @@
         <v>45359</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -30863,7 +30863,7 @@
         <v>45467</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45895</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -31009,7 +31009,7 @@
         <v>45825</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -31082,7 +31082,7 @@
         <v>45714</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -31155,7 +31155,7 @@
         <v>45587</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45762</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -31301,7 +31301,7 @@
         <v>46315</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -31374,7 +31374,7 @@
         <v>45789</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>46317</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -31520,7 +31520,7 @@
         <v>45439</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -31593,7 +31593,7 @@
         <v>45595</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>45594</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -31739,7 +31739,7 @@
         <v>46317</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -31817,7 +31817,7 @@
         <v>46317</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -31895,7 +31895,7 @@
         <v>46317</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -31973,7 +31973,7 @@
         <v>45679</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -32046,7 +32046,7 @@
         <v>45679</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -32119,7 +32119,7 @@
         <v>45544</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45399</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45070</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45377</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45097</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -32484,7 +32484,7 @@
         <v>45624</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -32557,7 +32557,7 @@
         <v>44665</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>45629</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -32703,7 +32703,7 @@
         <v>45629</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45390</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45266</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -32927,7 +32927,7 @@
         <v>46160</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -33000,7 +33000,7 @@
         <v>46160</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>46160</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>45301</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>44965</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -33292,7 +33292,7 @@
         <v>44699</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>45625</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -33438,7 +33438,7 @@
         <v>45131</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -33511,7 +33511,7 @@
         <v>45174</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -33584,7 +33584,7 @@
         <v>44802</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -33657,7 +33657,7 @@
         <v>45701</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -33730,7 +33730,7 @@
         <v>45672</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45519</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -33876,7 +33876,7 @@
         <v>45096</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -33949,7 +33949,7 @@
         <v>45096</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>45005</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -34095,7 +34095,7 @@
         <v>45740</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -34168,7 +34168,7 @@
         <v>45140</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>45722</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -34314,7 +34314,7 @@
         <v>45715</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -34387,7 +34387,7 @@
         <v>45035</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -34460,7 +34460,7 @@
         <v>45679</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -34533,7 +34533,7 @@
         <v>44831</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>44831</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -34679,7 +34679,7 @@
         <v>45093</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45740</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -34825,7 +34825,7 @@
         <v>45070</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -34898,7 +34898,7 @@
         <v>44537</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -34971,7 +34971,7 @@
         <v>45251</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>44851</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>44867</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45551</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -35263,7 +35263,7 @@
         <v>45035</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45035</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -35409,7 +35409,7 @@
         <v>44522</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44882</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>45096</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -35628,7 +35628,7 @@
         <v>45751</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -35706,7 +35706,7 @@
         <v>44586</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -35779,7 +35779,7 @@
         <v>45763</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -35852,7 +35852,7 @@
         <v>45763</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -35925,7 +35925,7 @@
         <v>45196</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45574</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>44552</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -36144,7 +36144,7 @@
         <v>45002</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45270</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45096</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>45424</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -36436,7 +36436,7 @@
         <v>45544</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -36514,7 +36514,7 @@
         <v>45574</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -36587,7 +36587,7 @@
         <v>45306</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -36660,7 +36660,7 @@
         <v>45394</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -36733,7 +36733,7 @@
         <v>45328</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -36811,7 +36811,7 @@
         <v>45316</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -36884,7 +36884,7 @@
         <v>45187</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>44544</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -37030,7 +37030,7 @@
         <v>45392</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45392</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -37176,7 +37176,7 @@
         <v>45334</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -37249,7 +37249,7 @@
         <v>45394</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -37322,7 +37322,7 @@
         <v>44656</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -37395,7 +37395,7 @@
         <v>45644</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -37468,7 +37468,7 @@
         <v>45734</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -37541,7 +37541,7 @@
         <v>45377</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>45673</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -37687,7 +37687,7 @@
         <v>45701</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>44622</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -37833,7 +37833,7 @@
         <v>44622</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45316</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -37979,7 +37979,7 @@
         <v>45316</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -38052,7 +38052,7 @@
         <v>44649</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45572</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -38198,7 +38198,7 @@
         <v>45736</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45747</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -38344,7 +38344,7 @@
         <v>45747</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -38417,7 +38417,7 @@
         <v>45716</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -38495,7 +38495,7 @@
         <v>45196</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -38568,7 +38568,7 @@
         <v>45673</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45547</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -38719,7 +38719,7 @@
         <v>45656</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>44819</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -38865,7 +38865,7 @@
         <v>44679</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>45096</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>45096</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45096</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>45713</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -39240,7 +39240,7 @@
         <v>45701</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -39313,7 +39313,7 @@
         <v>45694</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>44720</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -39464,7 +39464,7 @@
         <v>45572</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -39537,7 +39537,7 @@
         <v>44596</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -39615,7 +39615,7 @@
         <v>45113</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -39688,7 +39688,7 @@
         <v>45258</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>45157</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -39834,7 +39834,7 @@
         <v>44799</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>45169</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -39980,7 +39980,7 @@
         <v>44748</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -40058,7 +40058,7 @@
         <v>45761</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -40131,7 +40131,7 @@
         <v>44725</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -40204,7 +40204,7 @@
         <v>45315</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45624</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -40350,7 +40350,7 @@
         <v>45716</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -40423,7 +40423,7 @@
         <v>45315</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -40496,7 +40496,7 @@
         <v>45210</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -40569,7 +40569,7 @@
         <v>45267</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -40642,7 +40642,7 @@
         <v>45227</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>45301</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>45740</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45258</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -40934,7 +40934,7 @@
         <v>44952</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45747</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45747</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -41153,7 +41153,7 @@
         <v>45747</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -41226,7 +41226,7 @@
         <v>45259</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -41299,7 +41299,7 @@
         <v>45245</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45450</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -41450,7 +41450,7 @@
         <v>45376</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -41523,7 +41523,7 @@
         <v>44904</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -41596,7 +41596,7 @@
         <v>44732</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45547</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -41747,7 +41747,7 @@
         <v>45566</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -41820,7 +41820,7 @@
         <v>44511</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -41893,7 +41893,7 @@
         <v>45316</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -41966,7 +41966,7 @@
         <v>44867</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -42039,7 +42039,7 @@
         <v>45568</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -42112,7 +42112,7 @@
         <v>44578</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>45394</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -42258,7 +42258,7 @@
         <v>44735</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -42331,7 +42331,7 @@
         <v>44735</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -42404,7 +42404,7 @@
         <v>44735</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -42477,7 +42477,7 @@
         <v>45389</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -42550,7 +42550,7 @@
         <v>45454</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>45422</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>44767</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>45104</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45104</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>45385</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45422</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>45422</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>44865</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>45769</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45820</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -43353,7 +43353,7 @@
         <v>45667</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -43426,7 +43426,7 @@
         <v>45677</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>45638</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>45685</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>45881</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>45740</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -43791,7 +43791,7 @@
         <v>44866</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>46049</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -43937,7 +43937,7 @@
         <v>46092</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -44010,7 +44010,7 @@
         <v>46092</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -44083,7 +44083,7 @@
         <v>46114</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -44156,7 +44156,7 @@
         <v>45775</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -44229,7 +44229,7 @@
         <v>46274</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
